--- a/Versão5/SIS/Ontologia_Eletrica.xlsx
+++ b/Versão5/SIS/Ontologia_Eletrica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541580D7-EFE6-4BC7-903F-F865E63FD51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFE94B8-5013-456F-B878-AE99D735A08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3100" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3172" uniqueCount="811">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2450,13 +2450,61 @@
     <t>Atributo IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parâmetro Rvt</t>
   </si>
   <si>
     <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>De.Elétrica</t>
+  </si>
+  <si>
+    <t>Circuitos</t>
+  </si>
+  <si>
+    <t>Alta.Tensão</t>
+  </si>
+  <si>
+    <t>Média.Tensão</t>
+  </si>
+  <si>
+    <t>Baixa.Tensão</t>
+  </si>
+  <si>
+    <t>Elétrica.AT</t>
+  </si>
+  <si>
+    <t>Elétrica.BT</t>
+  </si>
+  <si>
+    <t>Elétrica.MT</t>
+  </si>
+  <si>
+    <t>Instalação elétrica de alta tensão</t>
+  </si>
+  <si>
+    <t>Instalação elétrica de baixa tensão</t>
+  </si>
+  <si>
+    <t>Instalação elétrica de média tensão</t>
   </si>
 </sst>
 </file>
@@ -2547,7 +2595,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2686,6 +2734,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -2799,7 +2853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3001,11 +3055,142 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="85">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3080,6 +3265,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3137,14 +3330,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3722,14 +3907,6 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4163,14 +4340,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="2" width="33.69140625" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>43</v>
       </c>
@@ -4181,7 +4358,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
@@ -4192,7 +4369,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>47</v>
       </c>
@@ -4203,7 +4380,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>48</v>
       </c>
@@ -4214,7 +4391,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>49</v>
       </c>
@@ -4226,7 +4403,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -4238,7 +4415,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
@@ -4249,7 +4426,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
         <v>53</v>
       </c>
@@ -4260,7 +4437,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>54</v>
       </c>
@@ -4271,7 +4448,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>56</v>
       </c>
@@ -4282,7 +4459,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -4293,7 +4470,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
@@ -4304,7 +4481,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>60</v>
       </c>
@@ -4315,7 +4492,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
@@ -4326,7 +4503,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>62</v>
       </c>
@@ -4337,7 +4514,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>63</v>
       </c>
@@ -4348,7 +4525,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -4359,19 +4536,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46253.814378819443</v>
+        <v>46260.368866898149</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>66</v>
       </c>
@@ -4382,7 +4559,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>68</v>
       </c>
@@ -4393,7 +4570,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>69</v>
       </c>
@@ -4404,7 +4581,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>70</v>
       </c>
@@ -4415,7 +4592,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>71</v>
       </c>
@@ -4426,7 +4603,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="39" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -4446,39 +4623,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC137"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC141"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.765625" style="61" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.15234375" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.765625" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.15234375" style="61" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="52.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="53.61328125" style="61" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="48.3828125" style="61" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.765625" style="61" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.921875" style="61" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="40.4609375" style="61" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="61" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.84375" style="68" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6" style="61" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.23046875" style="61" bestFit="1" customWidth="1"/>
-    <col min="30" max="98" width="2.53515625" style="61" customWidth="1"/>
-    <col min="99" max="16384" width="9.15234375" style="61"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="67" customWidth="1"/>
+    <col min="7" max="11" width="7.28515625" style="61" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="72.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="66.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.7109375" style="61" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" style="61" customWidth="1"/>
+    <col min="27" max="27" width="23.85546875" style="68" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.28515625" style="61" customWidth="1"/>
+    <col min="29" max="29" width="8.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="98" width="2.5703125" style="61" customWidth="1"/>
+    <col min="99" max="16384" width="9.140625" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="43.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="43.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>90</v>
       </c>
@@ -4552,10 +4729,10 @@
         <v>8</v>
       </c>
       <c r="Y1" s="36" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="Z1" s="36" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AA1" s="36" t="s">
         <v>790</v>
@@ -4567,7 +4744,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59">
         <v>2</v>
       </c>
@@ -4644,26 +4821,26 @@
         <v>109</v>
       </c>
       <c r="X2" s="60" t="str">
-        <f t="shared" ref="X2:X60" si="6">CONCATENATE("Key-ELET-",A2)</f>
+        <f t="shared" ref="X2:X65" si="6">CONCATENATE("Key-ELET-",A2)</f>
         <v>Key-ELET-2</v>
       </c>
       <c r="Y2" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="Z2" s="30" t="s">
-        <v>792</v>
+      <c r="Z2" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB2" s="30" t="s">
-        <v>792</v>
+      <c r="AB2" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59">
         <v>3</v>
       </c>
@@ -4746,20 +4923,20 @@
       <c r="Y3" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="Z3" s="30" t="s">
-        <v>792</v>
+      <c r="Z3" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB3" s="30" t="s">
-        <v>792</v>
+      <c r="AB3" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59">
         <v>4</v>
       </c>
@@ -4842,20 +5019,20 @@
       <c r="Y4" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="Z4" s="30" t="s">
-        <v>792</v>
+      <c r="Z4" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB4" s="30" t="s">
-        <v>792</v>
+      <c r="AB4" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59">
         <v>5</v>
       </c>
@@ -4938,20 +5115,20 @@
       <c r="Y5" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="Z5" s="30" t="s">
-        <v>792</v>
+      <c r="Z5" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB5" s="30" t="s">
-        <v>792</v>
+      <c r="AB5" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="59">
         <v>6</v>
       </c>
@@ -5034,20 +5211,20 @@
       <c r="Y6" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="Z6" s="30" t="s">
-        <v>792</v>
+      <c r="Z6" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="AB6" s="30" t="s">
-        <v>792</v>
+      <c r="AB6" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="59">
         <v>7</v>
       </c>
@@ -5130,20 +5307,20 @@
       <c r="Y7" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z7" s="30" t="s">
-        <v>792</v>
+      <c r="Z7" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB7" s="30" t="s">
-        <v>792</v>
+      <c r="AB7" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59">
         <v>8</v>
       </c>
@@ -5226,20 +5403,20 @@
       <c r="Y8" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z8" s="30" t="s">
-        <v>792</v>
+      <c r="Z8" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB8" s="30" t="s">
-        <v>792</v>
+      <c r="AB8" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="59">
         <v>9</v>
       </c>
@@ -5322,20 +5499,20 @@
       <c r="Y9" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z9" s="30" t="s">
-        <v>792</v>
+      <c r="Z9" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>682</v>
       </c>
-      <c r="AB9" s="30" t="s">
-        <v>792</v>
+      <c r="AB9" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="59">
         <v>10</v>
       </c>
@@ -5418,20 +5595,20 @@
       <c r="Y10" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z10" s="30" t="s">
-        <v>792</v>
+      <c r="Z10" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB10" s="30" t="s">
-        <v>792</v>
+      <c r="AB10" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="59">
         <v>11</v>
       </c>
@@ -5514,20 +5691,20 @@
       <c r="Y11" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z11" s="30" t="s">
-        <v>792</v>
+      <c r="Z11" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB11" s="30" t="s">
-        <v>792</v>
+      <c r="AB11" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="59">
         <v>12</v>
       </c>
@@ -5610,20 +5787,20 @@
       <c r="Y12" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z12" s="30" t="s">
-        <v>792</v>
+      <c r="Z12" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB12" s="30" t="s">
-        <v>792</v>
+      <c r="AB12" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="59">
         <v>13</v>
       </c>
@@ -5706,20 +5883,20 @@
       <c r="Y13" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z13" s="30" t="s">
-        <v>792</v>
+      <c r="Z13" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>683</v>
       </c>
-      <c r="AB13" s="30" t="s">
-        <v>792</v>
+      <c r="AB13" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="59">
         <v>14</v>
       </c>
@@ -5802,20 +5979,20 @@
       <c r="Y14" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z14" s="30" t="s">
-        <v>792</v>
+      <c r="Z14" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB14" s="30" t="s">
-        <v>792</v>
+      <c r="AB14" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="59">
         <v>15</v>
       </c>
@@ -5898,20 +6075,20 @@
       <c r="Y15" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z15" s="30" t="s">
-        <v>792</v>
+      <c r="Z15" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB15" s="30" t="s">
-        <v>792</v>
+      <c r="AB15" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="59">
         <v>16</v>
       </c>
@@ -5994,20 +6171,20 @@
       <c r="Y16" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z16" s="30" t="s">
-        <v>792</v>
+      <c r="Z16" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB16" s="30" t="s">
-        <v>792</v>
+      <c r="AB16" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="59">
         <v>17</v>
       </c>
@@ -6090,20 +6267,20 @@
       <c r="Y17" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z17" s="30" t="s">
-        <v>792</v>
+      <c r="Z17" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AB17" s="30" t="s">
-        <v>792</v>
+      <c r="AB17" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="59">
         <v>18</v>
       </c>
@@ -6186,20 +6363,20 @@
       <c r="Y18" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z18" s="30" t="s">
-        <v>792</v>
+      <c r="Z18" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="AB18" s="30" t="s">
-        <v>792</v>
+      <c r="AB18" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="59">
         <v>19</v>
       </c>
@@ -6282,20 +6459,20 @@
       <c r="Y19" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z19" s="30" t="s">
-        <v>792</v>
+      <c r="Z19" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="AB19" s="30" t="s">
-        <v>792</v>
+      <c r="AB19" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="59">
         <v>20</v>
       </c>
@@ -6379,20 +6556,20 @@
       <c r="Y20" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z20" s="30" t="s">
-        <v>792</v>
+      <c r="Z20" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>365</v>
       </c>
-      <c r="AB20" s="30" t="s">
-        <v>792</v>
+      <c r="AB20" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="59">
         <v>21</v>
       </c>
@@ -6476,20 +6653,20 @@
       <c r="Y21" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z21" s="30" t="s">
-        <v>792</v>
+      <c r="Z21" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="AB21" s="30" t="s">
-        <v>792</v>
+      <c r="AB21" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="59">
         <v>22</v>
       </c>
@@ -6573,20 +6750,20 @@
       <c r="Y22" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z22" s="30" t="s">
-        <v>792</v>
+      <c r="Z22" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>363</v>
       </c>
-      <c r="AB22" s="30" t="s">
-        <v>792</v>
+      <c r="AB22" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="59">
         <v>23</v>
       </c>
@@ -6670,20 +6847,20 @@
       <c r="Y23" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z23" s="30" t="s">
-        <v>792</v>
+      <c r="Z23" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="AB23" s="30" t="s">
-        <v>792</v>
+      <c r="AB23" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59">
         <v>24</v>
       </c>
@@ -6767,20 +6944,20 @@
       <c r="Y24" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z24" s="30" t="s">
-        <v>792</v>
+      <c r="Z24" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>361</v>
       </c>
-      <c r="AB24" s="30" t="s">
-        <v>792</v>
+      <c r="AB24" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="59">
         <v>25</v>
       </c>
@@ -6864,20 +7041,20 @@
       <c r="Y25" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z25" s="30" t="s">
-        <v>792</v>
+      <c r="Z25" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
         <v>360</v>
       </c>
-      <c r="AB25" s="30" t="s">
-        <v>792</v>
+      <c r="AB25" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="59">
         <v>26</v>
       </c>
@@ -6961,20 +7138,20 @@
       <c r="Y26" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z26" s="30" t="s">
-        <v>792</v>
+      <c r="Z26" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="29" t="s">
         <v>359</v>
       </c>
-      <c r="AB26" s="30" t="s">
-        <v>792</v>
+      <c r="AB26" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="59">
         <v>27</v>
       </c>
@@ -7058,20 +7235,20 @@
       <c r="Y27" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z27" s="30" t="s">
-        <v>792</v>
+      <c r="Z27" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB27" s="30" t="s">
-        <v>792</v>
+      <c r="AB27" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="59">
         <v>28</v>
       </c>
@@ -7155,20 +7332,20 @@
       <c r="Y28" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z28" s="30" t="s">
-        <v>792</v>
+      <c r="Z28" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB28" s="30" t="s">
-        <v>792</v>
+      <c r="AB28" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC28" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="59">
         <v>29</v>
       </c>
@@ -7252,20 +7429,20 @@
       <c r="Y29" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z29" s="30" t="s">
-        <v>792</v>
+      <c r="Z29" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB29" s="30" t="s">
-        <v>792</v>
+      <c r="AB29" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC29" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="59">
         <v>30</v>
       </c>
@@ -7349,20 +7526,20 @@
       <c r="Y30" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z30" s="30" t="s">
-        <v>792</v>
+      <c r="Z30" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB30" s="30" t="s">
-        <v>792</v>
+      <c r="AB30" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC30" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="59">
         <v>31</v>
       </c>
@@ -7446,20 +7623,20 @@
       <c r="Y31" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z31" s="30" t="s">
-        <v>792</v>
+      <c r="Z31" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB31" s="30" t="s">
-        <v>792</v>
+      <c r="AB31" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC31" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="59">
         <v>32</v>
       </c>
@@ -7543,20 +7720,20 @@
       <c r="Y32" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z32" s="30" t="s">
-        <v>792</v>
+      <c r="Z32" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA32" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB32" s="30" t="s">
-        <v>792</v>
+      <c r="AB32" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC32" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="59">
         <v>33</v>
       </c>
@@ -7640,20 +7817,20 @@
       <c r="Y33" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="Z33" s="30" t="s">
-        <v>792</v>
+      <c r="Z33" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA33" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="AB33" s="30" t="s">
-        <v>792</v>
+      <c r="AB33" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC33" s="30" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="59">
         <v>34</v>
       </c>
@@ -7737,20 +7914,20 @@
       <c r="Y34" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z34" s="30" t="s">
-        <v>792</v>
+      <c r="Z34" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="29" t="s">
         <v>628</v>
       </c>
-      <c r="AB34" s="30" t="s">
-        <v>792</v>
+      <c r="AB34" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC34" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="59">
         <v>35</v>
       </c>
@@ -7834,20 +8011,20 @@
       <c r="Y35" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z35" s="30" t="s">
-        <v>792</v>
+      <c r="Z35" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="29" t="s">
         <v>629</v>
       </c>
-      <c r="AB35" s="30" t="s">
-        <v>792</v>
+      <c r="AB35" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC35" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="59">
         <v>36</v>
       </c>
@@ -7931,20 +8108,20 @@
       <c r="Y36" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z36" s="30" t="s">
-        <v>792</v>
+      <c r="Z36" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA36" s="29" t="s">
         <v>630</v>
       </c>
-      <c r="AB36" s="30" t="s">
-        <v>792</v>
+      <c r="AB36" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC36" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="59">
         <v>37</v>
       </c>
@@ -8028,20 +8205,20 @@
       <c r="Y37" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z37" s="30" t="s">
-        <v>792</v>
+      <c r="Z37" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA37" s="29" t="s">
         <v>647</v>
       </c>
-      <c r="AB37" s="30" t="s">
-        <v>792</v>
+      <c r="AB37" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC37" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59">
         <v>38</v>
       </c>
@@ -8125,20 +8302,20 @@
       <c r="Y38" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z38" s="30" t="s">
-        <v>792</v>
+      <c r="Z38" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA38" s="29" t="s">
         <v>646</v>
       </c>
-      <c r="AB38" s="30" t="s">
-        <v>792</v>
+      <c r="AB38" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC38" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="59">
         <v>39</v>
       </c>
@@ -8222,20 +8399,20 @@
       <c r="Y39" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z39" s="30" t="s">
-        <v>792</v>
+      <c r="Z39" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA39" s="29" t="s">
         <v>645</v>
       </c>
-      <c r="AB39" s="30" t="s">
-        <v>792</v>
+      <c r="AB39" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC39" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="59">
         <v>40</v>
       </c>
@@ -8319,20 +8496,20 @@
       <c r="Y40" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z40" s="30" t="s">
-        <v>792</v>
+      <c r="Z40" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA40" s="58" t="s">
         <v>644</v>
       </c>
-      <c r="AB40" s="30" t="s">
-        <v>792</v>
+      <c r="AB40" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC40" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="59">
         <v>41</v>
       </c>
@@ -8416,20 +8593,20 @@
       <c r="Y41" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="Z41" s="30" t="s">
-        <v>792</v>
+      <c r="Z41" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA41" s="29" t="s">
         <v>643</v>
       </c>
-      <c r="AB41" s="30" t="s">
-        <v>792</v>
+      <c r="AB41" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC41" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="59">
         <v>42</v>
       </c>
@@ -8513,20 +8690,20 @@
       <c r="Y42" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z42" s="30" t="s">
-        <v>792</v>
+      <c r="Z42" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA42" s="29" t="s">
         <v>620</v>
       </c>
-      <c r="AB42" s="30" t="s">
-        <v>792</v>
+      <c r="AB42" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC42" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="59">
         <v>43</v>
       </c>
@@ -8610,20 +8787,20 @@
       <c r="Y43" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z43" s="30" t="s">
-        <v>792</v>
+      <c r="Z43" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA43" s="29" t="s">
         <v>621</v>
       </c>
-      <c r="AB43" s="30" t="s">
-        <v>792</v>
+      <c r="AB43" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC43" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="59">
         <v>44</v>
       </c>
@@ -8707,20 +8884,20 @@
       <c r="Y44" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z44" s="30" t="s">
-        <v>792</v>
+      <c r="Z44" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA44" s="29" t="s">
         <v>622</v>
       </c>
-      <c r="AB44" s="30" t="s">
-        <v>792</v>
+      <c r="AB44" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC44" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="59">
         <v>45</v>
       </c>
@@ -8804,20 +8981,20 @@
       <c r="Y45" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z45" s="30" t="s">
-        <v>792</v>
+      <c r="Z45" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA45" s="29" t="s">
         <v>624</v>
       </c>
-      <c r="AB45" s="30" t="s">
-        <v>792</v>
+      <c r="AB45" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC45" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="59">
         <v>46</v>
       </c>
@@ -8901,20 +9078,20 @@
       <c r="Y46" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z46" s="30" t="s">
-        <v>792</v>
+      <c r="Z46" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA46" s="29" t="s">
         <v>623</v>
       </c>
-      <c r="AB46" s="30" t="s">
-        <v>792</v>
+      <c r="AB46" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC46" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="59">
         <v>47</v>
       </c>
@@ -8998,20 +9175,20 @@
       <c r="Y47" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z47" s="30" t="s">
-        <v>792</v>
+      <c r="Z47" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA47" s="29" t="s">
         <v>625</v>
       </c>
-      <c r="AB47" s="30" t="s">
-        <v>792</v>
+      <c r="AB47" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC47" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="59">
         <v>48</v>
       </c>
@@ -9095,20 +9272,20 @@
       <c r="Y48" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z48" s="30" t="s">
-        <v>792</v>
+      <c r="Z48" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA48" s="29" t="s">
         <v>627</v>
       </c>
-      <c r="AB48" s="30" t="s">
-        <v>792</v>
+      <c r="AB48" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC48" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="59">
         <v>49</v>
       </c>
@@ -9192,20 +9369,20 @@
       <c r="Y49" s="29" t="s">
         <v>721</v>
       </c>
-      <c r="Z49" s="30" t="s">
-        <v>792</v>
+      <c r="Z49" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA49" s="29" t="s">
         <v>626</v>
       </c>
-      <c r="AB49" s="30" t="s">
-        <v>792</v>
+      <c r="AB49" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC49" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="59">
         <v>50</v>
       </c>
@@ -9289,20 +9466,20 @@
       <c r="Y50" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="Z50" s="30" t="s">
-        <v>792</v>
+      <c r="Z50" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA50" s="29" t="s">
         <v>635</v>
       </c>
-      <c r="AB50" s="30" t="s">
-        <v>792</v>
+      <c r="AB50" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC50" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="59">
         <v>51</v>
       </c>
@@ -9386,20 +9563,20 @@
       <c r="Y51" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="Z51" s="30" t="s">
-        <v>792</v>
+      <c r="Z51" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA51" s="29" t="s">
         <v>634</v>
       </c>
-      <c r="AB51" s="30" t="s">
-        <v>792</v>
+      <c r="AB51" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC51" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="59">
         <v>52</v>
       </c>
@@ -9483,20 +9660,20 @@
       <c r="Y52" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="Z52" s="30" t="s">
-        <v>792</v>
+      <c r="Z52" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA52" s="29" t="s">
         <v>633</v>
       </c>
-      <c r="AB52" s="30" t="s">
-        <v>792</v>
+      <c r="AB52" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC52" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="59">
         <v>53</v>
       </c>
@@ -9580,20 +9757,20 @@
       <c r="Y53" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="Z53" s="30" t="s">
-        <v>792</v>
+      <c r="Z53" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA53" s="29" t="s">
         <v>632</v>
       </c>
-      <c r="AB53" s="30" t="s">
-        <v>792</v>
+      <c r="AB53" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC53" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="59">
         <v>54</v>
       </c>
@@ -9677,20 +9854,20 @@
       <c r="Y54" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="Z54" s="30" t="s">
-        <v>792</v>
+      <c r="Z54" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA54" s="29" t="s">
         <v>631</v>
       </c>
-      <c r="AB54" s="30" t="s">
-        <v>792</v>
+      <c r="AB54" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC54" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="55" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="59">
         <v>55</v>
       </c>
@@ -9774,20 +9951,20 @@
       <c r="Y55" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z55" s="30" t="s">
-        <v>792</v>
+      <c r="Z55" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA55" s="29" t="s">
         <v>642</v>
       </c>
-      <c r="AB55" s="30" t="s">
-        <v>792</v>
+      <c r="AB55" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC55" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="56" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="59">
         <v>56</v>
       </c>
@@ -9871,20 +10048,20 @@
       <c r="Y56" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z56" s="30" t="s">
-        <v>792</v>
+      <c r="Z56" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA56" s="29" t="s">
         <v>641</v>
       </c>
-      <c r="AB56" s="30" t="s">
-        <v>792</v>
+      <c r="AB56" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC56" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="57" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="59">
         <v>57</v>
       </c>
@@ -9968,20 +10145,20 @@
       <c r="Y57" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z57" s="30" t="s">
-        <v>792</v>
+      <c r="Z57" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA57" s="29" t="s">
         <v>640</v>
       </c>
-      <c r="AB57" s="30" t="s">
-        <v>792</v>
+      <c r="AB57" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC57" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="58" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="59">
         <v>58</v>
       </c>
@@ -10065,20 +10242,20 @@
       <c r="Y58" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z58" s="30" t="s">
-        <v>792</v>
+      <c r="Z58" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA58" s="29" t="s">
         <v>639</v>
       </c>
-      <c r="AB58" s="30" t="s">
-        <v>792</v>
+      <c r="AB58" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC58" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="59" spans="1:29" s="66" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:29" s="66" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="59">
         <v>59</v>
       </c>
@@ -10162,20 +10339,20 @@
       <c r="Y59" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z59" s="30" t="s">
-        <v>792</v>
+      <c r="Z59" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA59" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="AB59" s="30" t="s">
-        <v>792</v>
+      <c r="AB59" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC59" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="59">
         <v>60</v>
       </c>
@@ -10259,20 +10436,20 @@
       <c r="Y60" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z60" s="30" t="s">
-        <v>792</v>
+      <c r="Z60" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA60" s="29" t="s">
         <v>637</v>
       </c>
-      <c r="AB60" s="30" t="s">
-        <v>792</v>
+      <c r="AB60" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC60" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="59">
         <v>61</v>
       </c>
@@ -10350,26 +10527,26 @@
         <v>109</v>
       </c>
       <c r="X61" s="60" t="str">
-        <f t="shared" ref="X61:X124" si="21">CONCATENATE("Key-ELET-",A61)</f>
+        <f t="shared" si="6"/>
         <v>Key-ELET-61</v>
       </c>
       <c r="Y61" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="Z61" s="30" t="s">
-        <v>792</v>
+      <c r="Z61" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA61" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="AB61" s="30" t="s">
-        <v>792</v>
+      <c r="AB61" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC61" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="59">
         <v>62</v>
       </c>
@@ -10446,26 +10623,26 @@
         <v>109</v>
       </c>
       <c r="X62" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>Key-ELET-62</v>
       </c>
       <c r="Y62" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z62" s="30" t="s">
-        <v>792</v>
+      <c r="Z62" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA62" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="AB62" s="30" t="s">
-        <v>792</v>
+      <c r="AB62" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC62" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="59">
         <v>63</v>
       </c>
@@ -10542,26 +10719,26 @@
         <v>109</v>
       </c>
       <c r="X63" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>Key-ELET-63</v>
       </c>
       <c r="Y63" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z63" s="30" t="s">
-        <v>792</v>
+      <c r="Z63" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA63" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="AB63" s="30" t="s">
-        <v>792</v>
+      <c r="AB63" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC63" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="59">
         <v>64</v>
       </c>
@@ -10638,26 +10815,26 @@
         <v>109</v>
       </c>
       <c r="X64" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>Key-ELET-64</v>
       </c>
       <c r="Y64" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z64" s="30" t="s">
-        <v>792</v>
+      <c r="Z64" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA64" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AB64" s="30" t="s">
-        <v>792</v>
+      <c r="AB64" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC64" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="59">
         <v>65</v>
       </c>
@@ -10692,15 +10869,15 @@
         <v>9</v>
       </c>
       <c r="L65" s="34" t="str">
-        <f t="shared" ref="L65:L128" si="22">CONCATENATE("", C65)</f>
+        <f t="shared" ref="L65:L128" si="21">CONCATENATE("", C65)</f>
         <v>EletroTécnicos</v>
       </c>
       <c r="M65" s="34" t="str">
-        <f t="shared" ref="M65:M80" si="23">CONCATENATE("", D65)</f>
+        <f t="shared" ref="M65:M80" si="22">CONCATENATE("", D65)</f>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N65" s="34" t="str">
-        <f t="shared" ref="N65:N128" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E65),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N65:N128" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E65),"."," ")," De "," de "))</f>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O65" s="30" t="str">
@@ -10734,26 +10911,26 @@
         <v>109</v>
       </c>
       <c r="X65" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="6"/>
         <v>Key-ELET-65</v>
       </c>
       <c r="Y65" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z65" s="30" t="s">
-        <v>792</v>
+      <c r="Z65" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA65" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="AB65" s="30" t="s">
-        <v>792</v>
+      <c r="AB65" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC65" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="59">
         <v>66</v>
       </c>
@@ -10788,15 +10965,15 @@
         <v>9</v>
       </c>
       <c r="L66" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M66" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M66" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N66" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N66" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O66" s="30" t="str">
@@ -10819,37 +10996,37 @@
         <v>143</v>
       </c>
       <c r="U66" s="30" t="str">
-        <f t="shared" ref="U66:V129" si="25">SUBSTITUTE(D66, "_", " ")</f>
+        <f t="shared" ref="U66:V129" si="24">SUBSTITUTE(D66, "_", " ")</f>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V66" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W66" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X66" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="X66:X129" si="25">CONCATENATE("Key-ELET-",A66)</f>
         <v>Key-ELET-66</v>
       </c>
       <c r="Y66" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z66" s="30" t="s">
-        <v>792</v>
+      <c r="Z66" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA66" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="AB66" s="30" t="s">
-        <v>792</v>
+      <c r="AB66" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC66" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="59">
         <v>67</v>
       </c>
@@ -10884,15 +11061,15 @@
         <v>9</v>
       </c>
       <c r="L67" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M67" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M67" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N67" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N67" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O67" s="30" t="str">
@@ -10915,37 +11092,37 @@
         <v>143</v>
       </c>
       <c r="U67" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V67" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W67" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X67" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-67</v>
       </c>
       <c r="Y67" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z67" s="30" t="s">
-        <v>792</v>
+      <c r="Z67" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA67" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB67" s="30" t="s">
-        <v>792</v>
+      <c r="AB67" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC67" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="59">
         <v>68</v>
       </c>
@@ -10980,15 +11157,15 @@
         <v>9</v>
       </c>
       <c r="L68" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M68" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M68" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N68" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N68" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O68" s="30" t="str">
@@ -11011,37 +11188,37 @@
         <v>143</v>
       </c>
       <c r="U68" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V68" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W68" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X68" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-68</v>
       </c>
       <c r="Y68" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z68" s="30" t="s">
-        <v>792</v>
+      <c r="Z68" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA68" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="AB68" s="30" t="s">
-        <v>792</v>
+      <c r="AB68" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC68" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="59">
         <v>69</v>
       </c>
@@ -11076,15 +11253,15 @@
         <v>9</v>
       </c>
       <c r="L69" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M69" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M69" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N69" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N69" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O69" s="30" t="str">
@@ -11107,37 +11284,37 @@
         <v>143</v>
       </c>
       <c r="U69" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V69" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W69" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X69" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-69</v>
       </c>
       <c r="Y69" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z69" s="30" t="s">
-        <v>792</v>
+      <c r="Z69" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA69" s="29" t="s">
         <v>249</v>
       </c>
-      <c r="AB69" s="30" t="s">
-        <v>792</v>
+      <c r="AB69" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC69" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="59">
         <v>70</v>
       </c>
@@ -11172,15 +11349,15 @@
         <v>9</v>
       </c>
       <c r="L70" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M70" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M70" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N70" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N70" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O70" s="30" t="str">
@@ -11203,37 +11380,37 @@
         <v>143</v>
       </c>
       <c r="U70" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V70" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W70" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X70" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-70</v>
       </c>
       <c r="Y70" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z70" s="30" t="s">
-        <v>792</v>
+      <c r="Z70" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA70" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="AB70" s="30" t="s">
-        <v>792</v>
+      <c r="AB70" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC70" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="59">
         <v>71</v>
       </c>
@@ -11268,15 +11445,15 @@
         <v>9</v>
       </c>
       <c r="L71" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M71" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M71" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N71" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N71" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O71" s="30" t="str">
@@ -11299,37 +11476,37 @@
         <v>143</v>
       </c>
       <c r="U71" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V71" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W71" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X71" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-71</v>
       </c>
       <c r="Y71" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z71" s="30" t="s">
-        <v>792</v>
+      <c r="Z71" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA71" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="AB71" s="30" t="s">
-        <v>792</v>
+      <c r="AB71" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC71" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="59">
         <v>72</v>
       </c>
@@ -11364,15 +11541,15 @@
         <v>9</v>
       </c>
       <c r="L72" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M72" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M72" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N72" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N72" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O72" s="30" t="str">
@@ -11395,37 +11572,37 @@
         <v>143</v>
       </c>
       <c r="U72" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V72" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W72" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X72" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-72</v>
       </c>
       <c r="Y72" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z72" s="30" t="s">
-        <v>792</v>
+      <c r="Z72" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA72" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="AB72" s="30" t="s">
-        <v>792</v>
+      <c r="AB72" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC72" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="59">
         <v>73</v>
       </c>
@@ -11460,15 +11637,15 @@
         <v>9</v>
       </c>
       <c r="L73" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M73" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M73" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N73" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N73" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O73" s="30" t="str">
@@ -11491,37 +11668,37 @@
         <v>143</v>
       </c>
       <c r="U73" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V73" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W73" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X73" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-73</v>
       </c>
       <c r="Y73" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z73" s="30" t="s">
-        <v>792</v>
+      <c r="Z73" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA73" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="AB73" s="30" t="s">
-        <v>792</v>
+      <c r="AB73" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC73" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="59">
         <v>74</v>
       </c>
@@ -11556,15 +11733,15 @@
         <v>9</v>
       </c>
       <c r="L74" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M74" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M74" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N74" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N74" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O74" s="30" t="str">
@@ -11587,37 +11764,37 @@
         <v>143</v>
       </c>
       <c r="U74" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V74" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W74" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X74" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-74</v>
       </c>
       <c r="Y74" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z74" s="30" t="s">
-        <v>792</v>
+      <c r="Z74" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA74" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="AB74" s="30" t="s">
-        <v>792</v>
+      <c r="AB74" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC74" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="59">
         <v>75</v>
       </c>
@@ -11652,15 +11829,15 @@
         <v>9</v>
       </c>
       <c r="L75" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M75" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M75" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N75" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N75" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O75" s="30" t="str">
@@ -11683,37 +11860,37 @@
         <v>143</v>
       </c>
       <c r="U75" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V75" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W75" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X75" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-75</v>
       </c>
       <c r="Y75" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z75" s="30" t="s">
-        <v>792</v>
+      <c r="Z75" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA75" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="AB75" s="30" t="s">
-        <v>792</v>
+      <c r="AB75" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC75" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="59">
         <v>76</v>
       </c>
@@ -11748,15 +11925,15 @@
         <v>9</v>
       </c>
       <c r="L76" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M76" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M76" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N76" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N76" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O76" s="30" t="str">
@@ -11779,37 +11956,37 @@
         <v>143</v>
       </c>
       <c r="U76" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V76" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W76" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X76" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-76</v>
       </c>
       <c r="Y76" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z76" s="30" t="s">
-        <v>792</v>
+      <c r="Z76" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA76" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="AB76" s="30" t="s">
-        <v>792</v>
+      <c r="AB76" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC76" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="59">
         <v>77</v>
       </c>
@@ -11844,15 +12021,15 @@
         <v>9</v>
       </c>
       <c r="L77" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M77" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M77" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N77" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N77" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O77" s="30" t="str">
@@ -11875,37 +12052,37 @@
         <v>143</v>
       </c>
       <c r="U77" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V77" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W77" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X77" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-77</v>
       </c>
       <c r="Y77" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z77" s="30" t="s">
-        <v>792</v>
+      <c r="Z77" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA77" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="AB77" s="30" t="s">
-        <v>792</v>
+      <c r="AB77" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC77" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="59">
         <v>78</v>
       </c>
@@ -11940,15 +12117,15 @@
         <v>9</v>
       </c>
       <c r="L78" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M78" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M78" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N78" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N78" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O78" s="30" t="str">
@@ -11971,37 +12148,37 @@
         <v>143</v>
       </c>
       <c r="U78" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V78" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W78" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X78" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-78</v>
       </c>
       <c r="Y78" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z78" s="30" t="s">
-        <v>792</v>
+      <c r="Z78" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA78" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="AB78" s="30" t="s">
-        <v>792</v>
+      <c r="AB78" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC78" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="59">
         <v>79</v>
       </c>
@@ -12036,15 +12213,15 @@
         <v>9</v>
       </c>
       <c r="L79" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M79" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M79" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N79" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N79" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Aparelhos Elétricos</v>
       </c>
       <c r="O79" s="30" t="str">
@@ -12067,37 +12244,37 @@
         <v>143</v>
       </c>
       <c r="U79" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V79" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Aparelhos.Elétricos</v>
       </c>
       <c r="W79" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X79" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-79</v>
       </c>
       <c r="Y79" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z79" s="30" t="s">
-        <v>792</v>
+      <c r="Z79" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA79" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="AB79" s="30" t="s">
-        <v>792</v>
+      <c r="AB79" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC79" s="30" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="59">
         <v>80</v>
       </c>
@@ -12132,15 +12309,15 @@
         <v>9</v>
       </c>
       <c r="L80" s="34" t="str">
+        <f t="shared" si="21"/>
+        <v>EletroTécnicos</v>
+      </c>
+      <c r="M80" s="34" t="str">
         <f t="shared" si="22"/>
-        <v>EletroTécnicos</v>
-      </c>
-      <c r="M80" s="34" t="str">
+        <v>Elementos.Elétricos</v>
+      </c>
+      <c r="N80" s="34" t="str">
         <f t="shared" si="23"/>
-        <v>Elementos.Elétricos</v>
-      </c>
-      <c r="N80" s="34" t="str">
-        <f t="shared" si="24"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O80" s="30" t="str">
@@ -12163,37 +12340,37 @@
         <v>143</v>
       </c>
       <c r="U80" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V80" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W80" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X80" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-80</v>
       </c>
       <c r="Y80" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z80" s="30" t="s">
-        <v>792</v>
+      <c r="Z80" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA80" s="29" t="s">
         <v>525</v>
       </c>
-      <c r="AB80" s="30" t="s">
-        <v>792</v>
+      <c r="AB80" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC80" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="59">
         <v>81</v>
       </c>
@@ -12228,7 +12405,7 @@
         <v>9</v>
       </c>
       <c r="L81" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M81" s="34" t="str">
@@ -12236,7 +12413,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N81" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O81" s="30" t="str">
@@ -12259,37 +12436,37 @@
         <v>143</v>
       </c>
       <c r="U81" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V81" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W81" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X81" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-81</v>
       </c>
       <c r="Y81" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z81" s="30" t="s">
-        <v>792</v>
+      <c r="Z81" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA81" s="29" t="s">
         <v>523</v>
       </c>
-      <c r="AB81" s="30" t="s">
-        <v>792</v>
+      <c r="AB81" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC81" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="59">
         <v>82</v>
       </c>
@@ -12324,7 +12501,7 @@
         <v>9</v>
       </c>
       <c r="L82" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M82" s="34" t="str">
@@ -12332,7 +12509,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N82" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O82" s="30" t="str">
@@ -12355,37 +12532,37 @@
         <v>143</v>
       </c>
       <c r="U82" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V82" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W82" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X82" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-82</v>
       </c>
       <c r="Y82" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z82" s="30" t="s">
-        <v>792</v>
+      <c r="Z82" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA82" s="29" t="s">
         <v>524</v>
       </c>
-      <c r="AB82" s="30" t="s">
-        <v>792</v>
+      <c r="AB82" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC82" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="59">
         <v>83</v>
       </c>
@@ -12420,7 +12597,7 @@
         <v>9</v>
       </c>
       <c r="L83" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M83" s="34" t="str">
@@ -12428,7 +12605,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N83" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O83" s="30" t="str">
@@ -12451,37 +12628,37 @@
         <v>143</v>
       </c>
       <c r="U83" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V83" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W83" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X83" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-83</v>
       </c>
       <c r="Y83" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z83" s="30" t="s">
-        <v>792</v>
+      <c r="Z83" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA83" s="29" t="s">
         <v>526</v>
       </c>
-      <c r="AB83" s="30" t="s">
-        <v>792</v>
+      <c r="AB83" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC83" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="59">
         <v>84</v>
       </c>
@@ -12516,7 +12693,7 @@
         <v>9</v>
       </c>
       <c r="L84" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M84" s="34" t="str">
@@ -12524,7 +12701,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N84" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O84" s="30" t="str">
@@ -12547,37 +12724,37 @@
         <v>143</v>
       </c>
       <c r="U84" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V84" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W84" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X84" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-84</v>
       </c>
       <c r="Y84" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z84" s="30" t="s">
-        <v>792</v>
+      <c r="Z84" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA84" s="29" t="s">
         <v>528</v>
       </c>
-      <c r="AB84" s="30" t="s">
-        <v>792</v>
+      <c r="AB84" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC84" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="59">
         <v>85</v>
       </c>
@@ -12612,7 +12789,7 @@
         <v>9</v>
       </c>
       <c r="L85" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M85" s="34" t="str">
@@ -12620,7 +12797,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N85" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O85" s="30" t="str">
@@ -12643,37 +12820,37 @@
         <v>143</v>
       </c>
       <c r="U85" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V85" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W85" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X85" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-85</v>
       </c>
       <c r="Y85" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z85" s="30" t="s">
-        <v>792</v>
+      <c r="Z85" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA85" s="29" t="s">
         <v>527</v>
       </c>
-      <c r="AB85" s="30" t="s">
-        <v>792</v>
+      <c r="AB85" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC85" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="59">
         <v>86</v>
       </c>
@@ -12708,7 +12885,7 @@
         <v>9</v>
       </c>
       <c r="L86" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M86" s="34" t="str">
@@ -12716,7 +12893,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N86" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O86" s="30" t="str">
@@ -12739,37 +12916,37 @@
         <v>143</v>
       </c>
       <c r="U86" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V86" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W86" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X86" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-86</v>
       </c>
       <c r="Y86" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z86" s="30" t="s">
-        <v>792</v>
+      <c r="Z86" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA86" s="29" t="s">
         <v>529</v>
       </c>
-      <c r="AB86" s="30" t="s">
-        <v>792</v>
+      <c r="AB86" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC86" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="59">
         <v>87</v>
       </c>
@@ -12804,7 +12981,7 @@
         <v>9</v>
       </c>
       <c r="L87" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M87" s="34" t="str">
@@ -12812,7 +12989,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N87" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O87" s="30" t="str">
@@ -12835,37 +13012,37 @@
         <v>143</v>
       </c>
       <c r="U87" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V87" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W87" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X87" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-87</v>
       </c>
       <c r="Y87" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z87" s="30" t="s">
-        <v>792</v>
+      <c r="Z87" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA87" s="29" t="s">
         <v>530</v>
       </c>
-      <c r="AB87" s="30" t="s">
-        <v>792</v>
+      <c r="AB87" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC87" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="59">
         <v>88</v>
       </c>
@@ -12900,7 +13077,7 @@
         <v>9</v>
       </c>
       <c r="L88" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M88" s="34" t="str">
@@ -12908,7 +13085,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N88" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O88" s="30" t="str">
@@ -12932,37 +13109,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U88" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V88" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W88" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X88" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-88</v>
       </c>
       <c r="Y88" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z88" s="30" t="s">
-        <v>792</v>
+      <c r="Z88" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA88" s="29" t="s">
         <v>552</v>
       </c>
-      <c r="AB88" s="30" t="s">
-        <v>792</v>
+      <c r="AB88" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC88" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="59">
         <v>89</v>
       </c>
@@ -12997,7 +13174,7 @@
         <v>9</v>
       </c>
       <c r="L89" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M89" s="34" t="str">
@@ -13005,7 +13182,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N89" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O89" s="30" t="str">
@@ -13029,37 +13206,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U89" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V89" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W89" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X89" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-89</v>
       </c>
       <c r="Y89" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z89" s="30" t="s">
-        <v>792</v>
+      <c r="Z89" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA89" s="29" t="s">
         <v>553</v>
       </c>
-      <c r="AB89" s="30" t="s">
-        <v>792</v>
+      <c r="AB89" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC89" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="59">
         <v>90</v>
       </c>
@@ -13094,7 +13271,7 @@
         <v>9</v>
       </c>
       <c r="L90" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M90" s="34" t="str">
@@ -13102,7 +13279,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N90" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O90" s="30" t="str">
@@ -13126,37 +13303,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U90" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V90" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W90" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X90" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-90</v>
       </c>
       <c r="Y90" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z90" s="30" t="s">
-        <v>792</v>
+      <c r="Z90" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA90" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="AB90" s="30" t="s">
-        <v>792</v>
+      <c r="AB90" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC90" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="59">
         <v>91</v>
       </c>
@@ -13191,7 +13368,7 @@
         <v>9</v>
       </c>
       <c r="L91" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M91" s="34" t="str">
@@ -13199,7 +13376,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N91" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O91" s="30" t="str">
@@ -13223,37 +13400,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U91" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V91" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W91" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X91" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-91</v>
       </c>
       <c r="Y91" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z91" s="30" t="s">
-        <v>792</v>
+      <c r="Z91" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA91" s="29" t="s">
         <v>554</v>
       </c>
-      <c r="AB91" s="30" t="s">
-        <v>792</v>
+      <c r="AB91" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC91" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="59">
         <v>92</v>
       </c>
@@ -13288,7 +13465,7 @@
         <v>9</v>
       </c>
       <c r="L92" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M92" s="34" t="str">
@@ -13296,7 +13473,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N92" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O92" s="30" t="str">
@@ -13320,37 +13497,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U92" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V92" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W92" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X92" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-92</v>
       </c>
       <c r="Y92" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z92" s="30" t="s">
-        <v>792</v>
+      <c r="Z92" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA92" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="AB92" s="30" t="s">
-        <v>792</v>
+      <c r="AB92" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC92" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="59">
         <v>93</v>
       </c>
@@ -13385,7 +13562,7 @@
         <v>9</v>
       </c>
       <c r="L93" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M93" s="34" t="str">
@@ -13393,7 +13570,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N93" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Força Motriz Elétrica</v>
       </c>
       <c r="O93" s="30" t="str">
@@ -13417,37 +13594,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U93" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V93" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Força.Motriz.Elétrica</v>
       </c>
       <c r="W93" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X93" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-93</v>
       </c>
       <c r="Y93" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z93" s="30" t="s">
-        <v>792</v>
+      <c r="Z93" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA93" s="29" t="s">
         <v>555</v>
       </c>
-      <c r="AB93" s="30" t="s">
-        <v>792</v>
+      <c r="AB93" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC93" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="59">
         <v>94</v>
       </c>
@@ -13482,7 +13659,7 @@
         <v>9</v>
       </c>
       <c r="L94" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M94" s="34" t="str">
@@ -13490,7 +13667,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N94" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O94" s="30" t="str">
@@ -13513,37 +13690,37 @@
         <v>143</v>
       </c>
       <c r="U94" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V94" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W94" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X94" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-94</v>
       </c>
       <c r="Y94" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z94" s="30" t="s">
-        <v>792</v>
+      <c r="Z94" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA94" s="29" t="s">
         <v>301</v>
       </c>
-      <c r="AB94" s="30" t="s">
-        <v>792</v>
+      <c r="AB94" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC94" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="59">
         <v>95</v>
       </c>
@@ -13578,7 +13755,7 @@
         <v>9</v>
       </c>
       <c r="L95" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M95" s="34" t="str">
@@ -13586,7 +13763,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N95" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O95" s="30" t="str">
@@ -13609,37 +13786,37 @@
         <v>143</v>
       </c>
       <c r="U95" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V95" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W95" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X95" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-95</v>
       </c>
       <c r="Y95" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z95" s="30" t="s">
-        <v>792</v>
+      <c r="Z95" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA95" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="AB95" s="30" t="s">
-        <v>792</v>
+      <c r="AB95" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC95" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="59">
         <v>96</v>
       </c>
@@ -13674,7 +13851,7 @@
         <v>9</v>
       </c>
       <c r="L96" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M96" s="34" t="str">
@@ -13682,7 +13859,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N96" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O96" s="30" t="str">
@@ -13705,37 +13882,37 @@
         <v>143</v>
       </c>
       <c r="U96" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V96" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W96" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X96" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-96</v>
       </c>
       <c r="Y96" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z96" s="30" t="s">
-        <v>792</v>
+      <c r="Z96" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA96" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="AB96" s="30" t="s">
-        <v>792</v>
+      <c r="AB96" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC96" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="59">
         <v>97</v>
       </c>
@@ -13770,7 +13947,7 @@
         <v>9</v>
       </c>
       <c r="L97" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M97" s="34" t="str">
@@ -13778,7 +13955,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N97" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O97" s="30" t="str">
@@ -13801,37 +13978,37 @@
         <v>143</v>
       </c>
       <c r="U97" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V97" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W97" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X97" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-97</v>
       </c>
       <c r="Y97" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z97" s="30" t="s">
-        <v>792</v>
+      <c r="Z97" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA97" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="AB97" s="30" t="s">
-        <v>792</v>
+      <c r="AB97" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC97" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="59">
         <v>98</v>
       </c>
@@ -13866,7 +14043,7 @@
         <v>9</v>
       </c>
       <c r="L98" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M98" s="34" t="str">
@@ -13874,7 +14051,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N98" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O98" s="30" t="str">
@@ -13897,37 +14074,37 @@
         <v>143</v>
       </c>
       <c r="U98" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V98" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W98" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X98" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-98</v>
       </c>
       <c r="Y98" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z98" s="30" t="s">
-        <v>792</v>
+      <c r="Z98" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA98" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="AB98" s="30" t="s">
-        <v>792</v>
+      <c r="AB98" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC98" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="59">
         <v>99</v>
       </c>
@@ -13962,7 +14139,7 @@
         <v>9</v>
       </c>
       <c r="L99" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M99" s="34" t="str">
@@ -13970,7 +14147,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N99" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O99" s="30" t="str">
@@ -13993,37 +14170,37 @@
         <v>143</v>
       </c>
       <c r="U99" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V99" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W99" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X99" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-99</v>
       </c>
       <c r="Y99" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z99" s="30" t="s">
-        <v>792</v>
+      <c r="Z99" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA99" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="AB99" s="30" t="s">
-        <v>792</v>
+      <c r="AB99" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC99" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="59">
         <v>100</v>
       </c>
@@ -14058,7 +14235,7 @@
         <v>9</v>
       </c>
       <c r="L100" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M100" s="34" t="str">
@@ -14066,7 +14243,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N100" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O100" s="30" t="str">
@@ -14089,37 +14266,37 @@
         <v>143</v>
       </c>
       <c r="U100" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V100" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W100" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X100" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-100</v>
       </c>
       <c r="Y100" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z100" s="30" t="s">
-        <v>792</v>
+      <c r="Z100" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA100" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="AB100" s="30" t="s">
-        <v>792</v>
+      <c r="AB100" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC100" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="59">
         <v>101</v>
       </c>
@@ -14154,7 +14331,7 @@
         <v>9</v>
       </c>
       <c r="L101" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M101" s="34" t="str">
@@ -14162,7 +14339,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N101" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O101" s="30" t="str">
@@ -14185,37 +14362,37 @@
         <v>143</v>
       </c>
       <c r="U101" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V101" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W101" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X101" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-101</v>
       </c>
       <c r="Y101" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z101" s="30" t="s">
-        <v>792</v>
+      <c r="Z101" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA101" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="AB101" s="30" t="s">
-        <v>792</v>
+      <c r="AB101" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC101" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="59">
         <v>102</v>
       </c>
@@ -14250,7 +14427,7 @@
         <v>9</v>
       </c>
       <c r="L102" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M102" s="34" t="str">
@@ -14258,7 +14435,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N102" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Baterias Elétricas</v>
       </c>
       <c r="O102" s="30" t="str">
@@ -14281,37 +14458,37 @@
         <v>143</v>
       </c>
       <c r="U102" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V102" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Baterias.Elétricas</v>
       </c>
       <c r="W102" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X102" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-102</v>
       </c>
       <c r="Y102" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z102" s="30" t="s">
-        <v>792</v>
+      <c r="Z102" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA102" s="29" t="s">
         <v>309</v>
       </c>
-      <c r="AB102" s="30" t="s">
-        <v>792</v>
+      <c r="AB102" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC102" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="59">
         <v>103</v>
       </c>
@@ -14346,7 +14523,7 @@
         <v>9</v>
       </c>
       <c r="L103" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M103" s="34" t="str">
@@ -14354,7 +14531,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N103" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O103" s="30" t="str">
@@ -14378,37 +14555,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U103" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V103" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W103" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X103" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-103</v>
       </c>
       <c r="Y103" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z103" s="30" t="s">
-        <v>792</v>
+      <c r="Z103" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA103" s="29" t="s">
         <v>383</v>
       </c>
-      <c r="AB103" s="30" t="s">
-        <v>792</v>
+      <c r="AB103" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC103" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="59">
         <v>104</v>
       </c>
@@ -14443,7 +14620,7 @@
         <v>9</v>
       </c>
       <c r="L104" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M104" s="34" t="str">
@@ -14451,7 +14628,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N104" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O104" s="30" t="str">
@@ -14475,37 +14652,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U104" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V104" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W104" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X104" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-104</v>
       </c>
       <c r="Y104" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z104" s="30" t="s">
-        <v>792</v>
+      <c r="Z104" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA104" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="AB104" s="30" t="s">
-        <v>792</v>
+      <c r="AB104" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC104" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="59">
         <v>105</v>
       </c>
@@ -14540,7 +14717,7 @@
         <v>9</v>
       </c>
       <c r="L105" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M105" s="34" t="str">
@@ -14548,7 +14725,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N105" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O105" s="30" t="str">
@@ -14572,37 +14749,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U105" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V105" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W105" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X105" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-105</v>
       </c>
       <c r="Y105" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z105" s="30" t="s">
-        <v>792</v>
+      <c r="Z105" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA105" s="29" t="s">
         <v>379</v>
       </c>
-      <c r="AB105" s="30" t="s">
-        <v>792</v>
+      <c r="AB105" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC105" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="59">
         <v>106</v>
       </c>
@@ -14637,7 +14814,7 @@
         <v>9</v>
       </c>
       <c r="L106" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M106" s="34" t="str">
@@ -14645,7 +14822,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N106" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O106" s="30" t="str">
@@ -14669,37 +14846,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U106" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V106" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W106" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X106" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-106</v>
       </c>
       <c r="Y106" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z106" s="30" t="s">
-        <v>792</v>
+      <c r="Z106" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA106" s="29" t="s">
         <v>382</v>
       </c>
-      <c r="AB106" s="30" t="s">
-        <v>792</v>
+      <c r="AB106" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC106" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="59">
         <v>107</v>
       </c>
@@ -14777,26 +14954,26 @@
         <v>109</v>
       </c>
       <c r="X107" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-107</v>
       </c>
       <c r="Y107" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z107" s="30" t="s">
-        <v>792</v>
+      <c r="Z107" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA107" s="29" t="s">
         <v>380</v>
       </c>
-      <c r="AB107" s="30" t="s">
-        <v>792</v>
+      <c r="AB107" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC107" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="59">
         <v>108</v>
       </c>
@@ -14831,7 +15008,7 @@
         <v>9</v>
       </c>
       <c r="L108" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M108" s="34" t="str">
@@ -14839,7 +15016,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N108" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O108" s="30" t="str">
@@ -14863,37 +15040,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U108" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V108" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W108" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X108" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-108</v>
       </c>
       <c r="Y108" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z108" s="30" t="s">
-        <v>792</v>
+      <c r="Z108" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA108" s="29" t="s">
         <v>384</v>
       </c>
-      <c r="AB108" s="30" t="s">
-        <v>792</v>
+      <c r="AB108" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC108" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="59">
         <v>109</v>
       </c>
@@ -14928,7 +15105,7 @@
         <v>9</v>
       </c>
       <c r="L109" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M109" s="34" t="str">
@@ -14936,7 +15113,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N109" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O109" s="30" t="str">
@@ -14960,37 +15137,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U109" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V109" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W109" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X109" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-109</v>
       </c>
       <c r="Y109" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z109" s="30" t="s">
-        <v>792</v>
+      <c r="Z109" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA109" s="29" t="s">
         <v>386</v>
       </c>
-      <c r="AB109" s="30" t="s">
-        <v>792</v>
+      <c r="AB109" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC109" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="59">
         <v>110</v>
       </c>
@@ -15025,7 +15202,7 @@
         <v>9</v>
       </c>
       <c r="L110" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M110" s="34" t="str">
@@ -15033,7 +15210,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N110" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O110" s="30" t="str">
@@ -15057,37 +15234,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U110" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V110" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W110" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X110" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-110</v>
       </c>
       <c r="Y110" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z110" s="30" t="s">
-        <v>792</v>
+      <c r="Z110" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA110" s="29" t="s">
         <v>381</v>
       </c>
-      <c r="AB110" s="30" t="s">
-        <v>792</v>
+      <c r="AB110" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC110" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="59">
         <v>111</v>
       </c>
@@ -15122,7 +15299,7 @@
         <v>9</v>
       </c>
       <c r="L111" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M111" s="34" t="str">
@@ -15130,7 +15307,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N111" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O111" s="30" t="str">
@@ -15154,37 +15331,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U111" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V111" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W111" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X111" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-111</v>
       </c>
       <c r="Y111" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z111" s="30" t="s">
-        <v>792</v>
+      <c r="Z111" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA111" s="29" t="s">
         <v>385</v>
       </c>
-      <c r="AB111" s="30" t="s">
-        <v>792</v>
+      <c r="AB111" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC111" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="59">
         <v>112</v>
       </c>
@@ -15219,7 +15396,7 @@
         <v>9</v>
       </c>
       <c r="L112" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M112" s="34" t="str">
@@ -15227,7 +15404,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N112" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O112" s="30" t="str">
@@ -15251,37 +15428,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U112" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V112" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W112" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X112" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-112</v>
       </c>
       <c r="Y112" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z112" s="30" t="s">
-        <v>792</v>
+      <c r="Z112" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA112" s="29" t="s">
         <v>387</v>
       </c>
-      <c r="AB112" s="30" t="s">
-        <v>792</v>
+      <c r="AB112" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC112" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="59">
         <v>113</v>
       </c>
@@ -15316,7 +15493,7 @@
         <v>9</v>
       </c>
       <c r="L113" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M113" s="34" t="str">
@@ -15324,7 +15501,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N113" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O113" s="30" t="str">
@@ -15348,37 +15525,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U113" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V113" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W113" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X113" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-113</v>
       </c>
       <c r="Y113" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z113" s="30" t="s">
-        <v>792</v>
+      <c r="Z113" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA113" s="29" t="s">
         <v>377</v>
       </c>
-      <c r="AB113" s="30" t="s">
-        <v>792</v>
+      <c r="AB113" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC113" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="59">
         <v>114</v>
       </c>
@@ -15413,7 +15590,7 @@
         <v>9</v>
       </c>
       <c r="L114" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M114" s="34" t="str">
@@ -15421,7 +15598,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N114" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O114" s="30" t="str">
@@ -15445,37 +15622,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U114" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V114" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W114" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X114" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-114</v>
       </c>
       <c r="Y114" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z114" s="30" t="s">
-        <v>792</v>
+      <c r="Z114" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA114" s="29" t="s">
         <v>376</v>
       </c>
-      <c r="AB114" s="30" t="s">
-        <v>792</v>
+      <c r="AB114" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC114" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="59">
         <v>115</v>
       </c>
@@ -15510,7 +15687,7 @@
         <v>9</v>
       </c>
       <c r="L115" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M115" s="34" t="str">
@@ -15518,7 +15695,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N115" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O115" s="30" t="str">
@@ -15542,37 +15719,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U115" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V115" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W115" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X115" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-115</v>
       </c>
       <c r="Y115" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z115" s="30" t="s">
-        <v>792</v>
+      <c r="Z115" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA115" s="29" t="s">
         <v>375</v>
       </c>
-      <c r="AB115" s="30" t="s">
-        <v>792</v>
+      <c r="AB115" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC115" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="59">
         <v>116</v>
       </c>
@@ -15607,7 +15784,7 @@
         <v>9</v>
       </c>
       <c r="L116" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M116" s="34" t="str">
@@ -15615,7 +15792,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N116" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O116" s="30" t="str">
@@ -15639,37 +15816,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U116" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V116" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W116" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X116" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-116</v>
       </c>
       <c r="Y116" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z116" s="30" t="s">
-        <v>792</v>
+      <c r="Z116" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA116" s="29" t="s">
         <v>374</v>
       </c>
-      <c r="AB116" s="30" t="s">
-        <v>792</v>
+      <c r="AB116" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC116" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="59">
         <v>117</v>
       </c>
@@ -15704,7 +15881,7 @@
         <v>9</v>
       </c>
       <c r="L117" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M117" s="34" t="str">
@@ -15712,7 +15889,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N117" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O117" s="30" t="str">
@@ -15736,37 +15913,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U117" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V117" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W117" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X117" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-117</v>
       </c>
       <c r="Y117" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z117" s="30" t="s">
-        <v>792</v>
+      <c r="Z117" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA117" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="AB117" s="30" t="s">
-        <v>792</v>
+      <c r="AB117" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC117" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="59">
         <v>118</v>
       </c>
@@ -15801,7 +15978,7 @@
         <v>9</v>
       </c>
       <c r="L118" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M118" s="34" t="str">
@@ -15809,7 +15986,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N118" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Proteção Elétrica</v>
       </c>
       <c r="O118" s="30" t="str">
@@ -15833,37 +16010,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U118" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V118" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Proteção.Elétrica</v>
       </c>
       <c r="W118" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X118" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-118</v>
       </c>
       <c r="Y118" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z118" s="30" t="s">
-        <v>792</v>
+      <c r="Z118" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA118" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="AB118" s="30" t="s">
-        <v>792</v>
+      <c r="AB118" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC118" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="59">
         <v>119</v>
       </c>
@@ -15898,7 +16075,7 @@
         <v>9</v>
       </c>
       <c r="L119" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M119" s="34" t="str">
@@ -15906,7 +16083,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N119" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Elétrica</v>
       </c>
       <c r="O119" s="30" t="str">
@@ -15930,37 +16107,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U119" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V119" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Elétrica</v>
       </c>
       <c r="W119" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X119" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-119</v>
       </c>
       <c r="Y119" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z119" s="30" t="s">
-        <v>792</v>
+      <c r="Z119" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA119" s="29" t="s">
         <v>371</v>
       </c>
-      <c r="AB119" s="30" t="s">
-        <v>792</v>
+      <c r="AB119" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC119" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="59">
         <v>120</v>
       </c>
@@ -15995,7 +16172,7 @@
         <v>9</v>
       </c>
       <c r="L120" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M120" s="34" t="str">
@@ -16003,7 +16180,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N120" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Elétrica</v>
       </c>
       <c r="O120" s="30" t="str">
@@ -16027,37 +16204,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U120" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V120" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Elétrica</v>
       </c>
       <c r="W120" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X120" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-120</v>
       </c>
       <c r="Y120" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z120" s="30" t="s">
-        <v>792</v>
+      <c r="Z120" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA120" s="29" t="s">
         <v>370</v>
       </c>
-      <c r="AB120" s="30" t="s">
-        <v>792</v>
+      <c r="AB120" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC120" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="59">
         <v>121</v>
       </c>
@@ -16092,7 +16269,7 @@
         <v>9</v>
       </c>
       <c r="L121" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M121" s="34" t="str">
@@ -16100,7 +16277,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N121" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Elétrica</v>
       </c>
       <c r="O121" s="30" t="str">
@@ -16124,37 +16301,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U121" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V121" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Elétrica</v>
       </c>
       <c r="W121" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X121" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-121</v>
       </c>
       <c r="Y121" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z121" s="30" t="s">
-        <v>792</v>
+      <c r="Z121" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA121" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="AB121" s="30" t="s">
-        <v>792</v>
+      <c r="AB121" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC121" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="59">
         <v>122</v>
       </c>
@@ -16189,7 +16366,7 @@
         <v>9</v>
       </c>
       <c r="L122" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M122" s="34" t="str">
@@ -16197,7 +16374,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N122" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Elétrica</v>
       </c>
       <c r="O122" s="30" t="str">
@@ -16221,37 +16398,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U122" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V122" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Elétrica</v>
       </c>
       <c r="W122" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X122" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-122</v>
       </c>
       <c r="Y122" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z122" s="30" t="s">
-        <v>792</v>
+      <c r="Z122" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA122" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="AB122" s="30" t="s">
-        <v>792</v>
+      <c r="AB122" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC122" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="59">
         <v>123</v>
       </c>
@@ -16286,7 +16463,7 @@
         <v>9</v>
       </c>
       <c r="L123" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M123" s="34" t="str">
@@ -16294,7 +16471,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N123" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Solar</v>
       </c>
       <c r="O123" s="30" t="str">
@@ -16318,37 +16495,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U123" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V123" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Solar</v>
       </c>
       <c r="W123" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X123" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-123</v>
       </c>
       <c r="Y123" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z123" s="30" t="s">
-        <v>792</v>
+      <c r="Z123" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA123" s="29" t="s">
         <v>436</v>
       </c>
-      <c r="AB123" s="30" t="s">
-        <v>792</v>
+      <c r="AB123" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC123" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="59">
         <v>124</v>
       </c>
@@ -16383,7 +16560,7 @@
         <v>9</v>
       </c>
       <c r="L124" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M124" s="34" t="str">
@@ -16391,7 +16568,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N124" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Solar</v>
       </c>
       <c r="O124" s="30" t="str">
@@ -16415,37 +16592,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U124" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V124" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Solar</v>
       </c>
       <c r="W124" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X124" s="60" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-124</v>
       </c>
       <c r="Y124" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z124" s="30" t="s">
-        <v>792</v>
+      <c r="Z124" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA124" s="29" t="s">
         <v>438</v>
       </c>
-      <c r="AB124" s="30" t="s">
-        <v>792</v>
+      <c r="AB124" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC124" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="59">
         <v>125</v>
       </c>
@@ -16480,7 +16657,7 @@
         <v>9</v>
       </c>
       <c r="L125" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M125" s="34" t="str">
@@ -16488,7 +16665,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N125" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Geração Solar</v>
       </c>
       <c r="O125" s="30" t="str">
@@ -16512,37 +16689,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U125" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V125" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Geração.Solar</v>
       </c>
       <c r="W125" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X125" s="60" t="str">
-        <f t="shared" ref="X125:X137" si="43">CONCATENATE("Key-ELET-",A125)</f>
+        <f t="shared" si="25"/>
         <v>Key-ELET-125</v>
       </c>
       <c r="Y125" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z125" s="30" t="s">
-        <v>792</v>
+      <c r="Z125" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA125" s="29" t="s">
         <v>437</v>
       </c>
-      <c r="AB125" s="30" t="s">
-        <v>792</v>
+      <c r="AB125" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC125" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="59">
         <v>126</v>
       </c>
@@ -16577,7 +16754,7 @@
         <v>9</v>
       </c>
       <c r="L126" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M126" s="34" t="str">
@@ -16585,7 +16762,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N126" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Filtros Elétricos</v>
       </c>
       <c r="O126" s="30" t="str">
@@ -16609,37 +16786,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U126" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V126" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Filtros.Elétricos</v>
       </c>
       <c r="W126" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X126" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-126</v>
       </c>
       <c r="Y126" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z126" s="30" t="s">
-        <v>792</v>
+      <c r="Z126" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA126" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="AB126" s="30" t="s">
-        <v>792</v>
+      <c r="AB126" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC126" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="59">
         <v>127</v>
       </c>
@@ -16674,7 +16851,7 @@
         <v>9</v>
       </c>
       <c r="L127" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M127" s="34" t="str">
@@ -16682,7 +16859,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N127" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Filtros Elétricos</v>
       </c>
       <c r="O127" s="30" t="str">
@@ -16706,37 +16883,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U127" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V127" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Filtros.Elétricos</v>
       </c>
       <c r="W127" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X127" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-127</v>
       </c>
       <c r="Y127" s="30" t="s">
         <v>725</v>
       </c>
-      <c r="Z127" s="30" t="s">
-        <v>792</v>
+      <c r="Z127" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA127" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="AB127" s="30" t="s">
-        <v>792</v>
+      <c r="AB127" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC127" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="59">
         <v>128</v>
       </c>
@@ -16771,7 +16948,7 @@
         <v>9</v>
       </c>
       <c r="L128" s="34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M128" s="34" t="str">
@@ -16779,7 +16956,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N128" s="34" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O128" s="30" t="str">
@@ -16803,37 +16980,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U128" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V128" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Transformação.Elétrica</v>
       </c>
       <c r="W128" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X128" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-128</v>
       </c>
       <c r="Y128" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z128" s="30" t="s">
-        <v>792</v>
+      <c r="Z128" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA128" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="AB128" s="30" t="s">
-        <v>792</v>
+      <c r="AB128" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC128" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="59">
         <v>129</v>
       </c>
@@ -16868,7 +17045,7 @@
         <v>9</v>
       </c>
       <c r="L129" s="34" t="str">
-        <f t="shared" ref="L129:L137" si="44">CONCATENATE("", C129)</f>
+        <f t="shared" ref="L129:L137" si="43">CONCATENATE("", C129)</f>
         <v>EletroTécnicos</v>
       </c>
       <c r="M129" s="34" t="str">
@@ -16876,7 +17053,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N129" s="34" t="str">
-        <f t="shared" ref="N129:N137" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E129),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N129:N137" si="44">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E129),"."," ")," De "," de "))</f>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O129" s="30" t="str">
@@ -16900,37 +17077,37 @@
         <v>EletroTécnicos</v>
       </c>
       <c r="U129" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Elementos.Elétricos</v>
       </c>
       <c r="V129" s="30" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>Transformação.Elétrica</v>
       </c>
       <c r="W129" s="30" t="s">
         <v>109</v>
       </c>
       <c r="X129" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="25"/>
         <v>Key-ELET-129</v>
       </c>
       <c r="Y129" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z129" s="30" t="s">
-        <v>792</v>
+      <c r="Z129" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA129" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="AB129" s="30" t="s">
-        <v>792</v>
+      <c r="AB129" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC129" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="59">
         <v>130</v>
       </c>
@@ -16965,7 +17142,7 @@
         <v>9</v>
       </c>
       <c r="L130" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M130" s="34" t="str">
@@ -16973,7 +17150,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N130" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O130" s="30" t="str">
@@ -17008,26 +17185,26 @@
         <v>109</v>
       </c>
       <c r="X130" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="X130:X138" si="45">CONCATENATE("Key-ELET-",A130)</f>
         <v>Key-ELET-130</v>
       </c>
       <c r="Y130" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z130" s="30" t="s">
-        <v>792</v>
+      <c r="Z130" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA130" s="29" t="s">
         <v>356</v>
       </c>
-      <c r="AB130" s="30" t="s">
-        <v>792</v>
+      <c r="AB130" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC130" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="59">
         <v>131</v>
       </c>
@@ -17062,7 +17239,7 @@
         <v>9</v>
       </c>
       <c r="L131" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M131" s="34" t="str">
@@ -17070,7 +17247,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N131" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O131" s="30" t="str">
@@ -17105,26 +17282,26 @@
         <v>109</v>
       </c>
       <c r="X131" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-131</v>
       </c>
       <c r="Y131" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z131" s="30" t="s">
-        <v>792</v>
+      <c r="Z131" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA131" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="AB131" s="30" t="s">
-        <v>792</v>
+      <c r="AB131" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC131" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="59">
         <v>132</v>
       </c>
@@ -17159,7 +17336,7 @@
         <v>9</v>
       </c>
       <c r="L132" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M132" s="34" t="str">
@@ -17167,7 +17344,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N132" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O132" s="30" t="str">
@@ -17202,26 +17379,26 @@
         <v>109</v>
       </c>
       <c r="X132" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-132</v>
       </c>
       <c r="Y132" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z132" s="30" t="s">
-        <v>792</v>
+      <c r="Z132" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA132" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="AB132" s="30" t="s">
-        <v>792</v>
+      <c r="AB132" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC132" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="59">
         <v>133</v>
       </c>
@@ -17256,7 +17433,7 @@
         <v>9</v>
       </c>
       <c r="L133" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M133" s="34" t="str">
@@ -17264,7 +17441,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N133" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O133" s="30" t="str">
@@ -17299,26 +17476,26 @@
         <v>109</v>
       </c>
       <c r="X133" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-133</v>
       </c>
       <c r="Y133" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z133" s="30" t="s">
-        <v>792</v>
+      <c r="Z133" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA133" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="AB133" s="30" t="s">
-        <v>792</v>
+      <c r="AB133" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC133" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="59">
         <v>134</v>
       </c>
@@ -17353,7 +17530,7 @@
         <v>9</v>
       </c>
       <c r="L134" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M134" s="34" t="str">
@@ -17361,7 +17538,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N134" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O134" s="30" t="str">
@@ -17396,26 +17573,26 @@
         <v>109</v>
       </c>
       <c r="X134" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-134</v>
       </c>
       <c r="Y134" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z134" s="30" t="s">
-        <v>792</v>
+      <c r="Z134" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA134" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="AB134" s="30" t="s">
-        <v>792</v>
+      <c r="AB134" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC134" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="59">
         <v>135</v>
       </c>
@@ -17450,7 +17627,7 @@
         <v>9</v>
       </c>
       <c r="L135" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M135" s="34" t="str">
@@ -17458,7 +17635,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N135" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O135" s="30" t="str">
@@ -17493,26 +17670,26 @@
         <v>109</v>
       </c>
       <c r="X135" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-135</v>
       </c>
       <c r="Y135" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="Z135" s="30" t="s">
-        <v>792</v>
+      <c r="Z135" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA135" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="AB135" s="30" t="s">
-        <v>792</v>
+      <c r="AB135" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC135" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="59">
         <v>136</v>
       </c>
@@ -17547,7 +17724,7 @@
         <v>9</v>
       </c>
       <c r="L136" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M136" s="34" t="str">
@@ -17555,7 +17732,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N136" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Transformação Elétrica</v>
       </c>
       <c r="O136" s="30" t="str">
@@ -17590,26 +17767,26 @@
         <v>109</v>
       </c>
       <c r="X136" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-136</v>
       </c>
       <c r="Y136" s="30" t="s">
         <v>726</v>
       </c>
-      <c r="Z136" s="30" t="s">
-        <v>792</v>
+      <c r="Z136" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA136" s="30" t="s">
         <v>388</v>
       </c>
-      <c r="AB136" s="30" t="s">
-        <v>792</v>
+      <c r="AB136" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC136" s="30" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="59">
         <v>137</v>
       </c>
@@ -17644,7 +17821,7 @@
         <v>9</v>
       </c>
       <c r="L137" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>EletroTécnicos</v>
       </c>
       <c r="M137" s="34" t="str">
@@ -17652,7 +17829,7 @@
         <v>Elementos.Elétricos</v>
       </c>
       <c r="N137" s="34" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>Acessórios Elétricos</v>
       </c>
       <c r="O137" s="30" t="str">
@@ -17687,23 +17864,419 @@
         <v>109</v>
       </c>
       <c r="X137" s="60" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>Key-ELET-137</v>
       </c>
       <c r="Y137" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="Z137" s="30" t="s">
-        <v>792</v>
+      <c r="Z137" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AA137" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="AB137" s="30" t="s">
-        <v>792</v>
+      <c r="AB137" s="71" t="s">
+        <v>9</v>
       </c>
       <c r="AC137" s="30" t="s">
         <v>677</v>
+      </c>
+    </row>
+    <row r="138" spans="1:29" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="59">
+        <v>138</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C138" s="64" t="s">
+        <v>795</v>
+      </c>
+      <c r="D138" s="64" t="s">
+        <v>796</v>
+      </c>
+      <c r="E138" s="64" t="s">
+        <v>797</v>
+      </c>
+      <c r="F138" s="64" t="s">
+        <v>798</v>
+      </c>
+      <c r="G138" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="I138" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="J138" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="K138" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="L138" s="34" t="str">
+        <f t="shared" ref="L138:O138" si="48">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M138" s="34" t="str">
+        <f t="shared" si="48"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N138" s="34" t="str">
+        <f t="shared" si="48"/>
+        <v>Macros</v>
+      </c>
+      <c r="O138" s="34" t="str">
+        <f t="shared" si="48"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P138" s="30" t="s">
+        <v>799</v>
+      </c>
+      <c r="Q138" s="69" t="str">
+        <f t="shared" ref="Q138" si="49">_xlfn.TRANSLATE(P138,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R138" s="69" t="str">
+        <f t="shared" ref="R138" si="50">_xlfn.TRANSLATE(P138,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S138" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T138" s="30" t="str">
+        <f t="shared" ref="T138:V138" si="51">SUBSTITUTE(C138, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U138" s="30" t="str">
+        <f t="shared" si="51"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V138" s="70" t="str">
+        <f t="shared" si="51"/>
+        <v>Macros</v>
+      </c>
+      <c r="W138" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="X138" s="60" t="str">
+        <f t="shared" si="45"/>
+        <v>Key-ELET-138</v>
+      </c>
+      <c r="Y138" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z138" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA138" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB138" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC138" s="71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:29" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="59">
+        <v>139</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C139" s="64" t="s">
+        <v>800</v>
+      </c>
+      <c r="D139" s="64" t="s">
+        <v>802</v>
+      </c>
+      <c r="E139" s="64" t="s">
+        <v>801</v>
+      </c>
+      <c r="F139" s="64" t="s">
+        <v>805</v>
+      </c>
+      <c r="G139" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H139" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="I139" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="J139" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="K139" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="L139" s="34" t="str">
+        <f t="shared" ref="L139" si="52">SUBSTITUTE(CONCATENATE("", C139), ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="M139" s="34" t="str">
+        <f t="shared" ref="M139" si="53">SUBSTITUTE(CONCATENATE("", D139), ".", " ")</f>
+        <v>Alta Tensão</v>
+      </c>
+      <c r="N139" s="34" t="str">
+        <f t="shared" ref="N139" si="54">SUBSTITUTE(CONCATENATE("", E139), ".", " ")</f>
+        <v>Circuitos</v>
+      </c>
+      <c r="O139" s="34" t="str">
+        <f t="shared" ref="O139" si="55">SUBSTITUTE(CONCATENATE("", F139), ".", " ")</f>
+        <v>Elétrica AT</v>
+      </c>
+      <c r="P139" s="73" t="s">
+        <v>808</v>
+      </c>
+      <c r="Q139" s="69" t="str">
+        <f t="shared" ref="Q139" si="56">_xlfn.TRANSLATE(P139,"pt","es")</f>
+        <v>Instalación eléctrica de alta tensión</v>
+      </c>
+      <c r="R139" s="69" t="str">
+        <f t="shared" ref="R139" si="57">_xlfn.TRANSLATE(P139,"pt","en")</f>
+        <v>High voltage electrical installation</v>
+      </c>
+      <c r="S139" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T139" s="30" t="str">
+        <f t="shared" ref="T139" si="58">SUBSTITUTE(C139, ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="U139" s="30" t="str">
+        <f t="shared" ref="U139" si="59">SUBSTITUTE(D139, ".", " ")</f>
+        <v>Alta Tensão</v>
+      </c>
+      <c r="V139" s="70" t="str">
+        <f t="shared" ref="V139" si="60">SUBSTITUTE(E139, ".", " ")</f>
+        <v>Circuitos</v>
+      </c>
+      <c r="W139" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="X139" s="60" t="str">
+        <f t="shared" ref="X139" si="61">CONCATENATE("Key-ELET-",A139)</f>
+        <v>Key-ELET-139</v>
+      </c>
+      <c r="Y139" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z139" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA139" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB139" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC139" s="71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:29" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="59">
+        <v>140</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C140" s="64" t="s">
+        <v>800</v>
+      </c>
+      <c r="D140" s="64" t="s">
+        <v>803</v>
+      </c>
+      <c r="E140" s="64" t="s">
+        <v>801</v>
+      </c>
+      <c r="F140" s="64" t="s">
+        <v>807</v>
+      </c>
+      <c r="G140" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H140" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="I140" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="J140" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="K140" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="L140" s="34" t="str">
+        <f t="shared" ref="L140:L141" si="62">SUBSTITUTE(CONCATENATE("", C140), ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="M140" s="34" t="str">
+        <f t="shared" ref="M140:M141" si="63">SUBSTITUTE(CONCATENATE("", D140), ".", " ")</f>
+        <v>Média Tensão</v>
+      </c>
+      <c r="N140" s="34" t="str">
+        <f t="shared" ref="N140:N141" si="64">SUBSTITUTE(CONCATENATE("", E140), ".", " ")</f>
+        <v>Circuitos</v>
+      </c>
+      <c r="O140" s="34" t="str">
+        <f t="shared" ref="O140:O141" si="65">SUBSTITUTE(CONCATENATE("", F140), ".", " ")</f>
+        <v>Elétrica MT</v>
+      </c>
+      <c r="P140" s="73" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q140" s="69" t="str">
+        <f t="shared" ref="Q140:Q141" si="66">_xlfn.TRANSLATE(P140,"pt","es")</f>
+        <v>Instalación eléctrica de media tensión</v>
+      </c>
+      <c r="R140" s="69" t="str">
+        <f t="shared" ref="R140:R141" si="67">_xlfn.TRANSLATE(P140,"pt","en")</f>
+        <v>Medium voltage electrical installation</v>
+      </c>
+      <c r="S140" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T140" s="30" t="str">
+        <f t="shared" ref="T140:T141" si="68">SUBSTITUTE(C140, ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="U140" s="30" t="str">
+        <f t="shared" ref="U140:U141" si="69">SUBSTITUTE(D140, ".", " ")</f>
+        <v>Média Tensão</v>
+      </c>
+      <c r="V140" s="70" t="str">
+        <f t="shared" ref="V140:V141" si="70">SUBSTITUTE(E140, ".", " ")</f>
+        <v>Circuitos</v>
+      </c>
+      <c r="W140" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="X140" s="60" t="str">
+        <f t="shared" ref="X140:X141" si="71">CONCATENATE("Key-ELET-",A140)</f>
+        <v>Key-ELET-140</v>
+      </c>
+      <c r="Y140" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z140" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA140" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB140" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC140" s="71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:29" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="59">
+        <v>141</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C141" s="64" t="s">
+        <v>800</v>
+      </c>
+      <c r="D141" s="64" t="s">
+        <v>804</v>
+      </c>
+      <c r="E141" s="64" t="s">
+        <v>801</v>
+      </c>
+      <c r="F141" s="64" t="s">
+        <v>806</v>
+      </c>
+      <c r="G141" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H141" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="I141" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="J141" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="K141" s="63" t="s">
+        <v>9</v>
+      </c>
+      <c r="L141" s="34" t="str">
+        <f t="shared" si="62"/>
+        <v>De Elétrica</v>
+      </c>
+      <c r="M141" s="34" t="str">
+        <f t="shared" si="63"/>
+        <v>Baixa Tensão</v>
+      </c>
+      <c r="N141" s="34" t="str">
+        <f t="shared" si="64"/>
+        <v>Circuitos</v>
+      </c>
+      <c r="O141" s="34" t="str">
+        <f t="shared" si="65"/>
+        <v>Elétrica BT</v>
+      </c>
+      <c r="P141" s="73" t="s">
+        <v>809</v>
+      </c>
+      <c r="Q141" s="69" t="str">
+        <f t="shared" si="66"/>
+        <v>Instalación eléctrica de bajo voltaje</v>
+      </c>
+      <c r="R141" s="69" t="str">
+        <f t="shared" si="67"/>
+        <v>Low voltage electrical installation</v>
+      </c>
+      <c r="S141" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T141" s="30" t="str">
+        <f t="shared" si="68"/>
+        <v>De Elétrica</v>
+      </c>
+      <c r="U141" s="30" t="str">
+        <f t="shared" si="69"/>
+        <v>Baixa Tensão</v>
+      </c>
+      <c r="V141" s="70" t="str">
+        <f t="shared" si="70"/>
+        <v>Circuitos</v>
+      </c>
+      <c r="W141" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="X141" s="60" t="str">
+        <f t="shared" si="71"/>
+        <v>Key-ELET-141</v>
+      </c>
+      <c r="Y141" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z141" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA141" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB141" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC141" s="71" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -17711,144 +18284,167 @@
     <sortCondition ref="F2:F215"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B137">
-    <cfRule type="cellIs" dxfId="73" priority="14" operator="equal">
+  <conditionalFormatting sqref="A2:B125 B126:B137 A126:A141">
+    <cfRule type="cellIs" dxfId="0" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:O1 S1:Y1 AC1">
-    <cfRule type="cellIs" dxfId="72" priority="397" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="408" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="71" priority="1833"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1844"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="70" priority="37"/>
+  <conditionalFormatting sqref="F1:F137 F142:F1048576">
+    <cfRule type="duplicateValues" dxfId="82" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="69" priority="1846"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="1857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F33">
-    <cfRule type="duplicateValues" dxfId="68" priority="2195"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="2206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F39">
-    <cfRule type="duplicateValues" dxfId="67" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="75"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F41">
-    <cfRule type="duplicateValues" dxfId="63" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42:F49">
-    <cfRule type="duplicateValues" dxfId="60" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="56" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="55" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="51" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="duplicateValues" dxfId="47" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="duplicateValues" dxfId="43" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F59 F42:F49">
-    <cfRule type="duplicateValues" dxfId="39" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F61 F42:F50">
-    <cfRule type="duplicateValues" dxfId="38" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60:F61">
-    <cfRule type="duplicateValues" dxfId="36" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F62:F80 F1:F33 F94:F1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="2200"/>
+  <conditionalFormatting sqref="F62:F80 F1:F33 F94:F137 F142:F1048576">
+    <cfRule type="duplicateValues" dxfId="47" priority="2211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88:F93">
-    <cfRule type="duplicateValues" dxfId="34" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="261"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94:F102">
-    <cfRule type="duplicateValues" dxfId="26" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1905"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104">
-    <cfRule type="duplicateValues" dxfId="25" priority="1956"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1967"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119:F136 F104">
-    <cfRule type="duplicateValues" dxfId="24" priority="2045"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="2056"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F119:F1048576 F104 F94:F102 F62:F80 F1:F33">
-    <cfRule type="duplicateValues" dxfId="23" priority="2206"/>
+  <conditionalFormatting sqref="F119:F137 F104 F94:F102 F62:F80 F1:F33 F142:F1048576">
+    <cfRule type="duplicateValues" dxfId="35" priority="2217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F136 F104">
-    <cfRule type="duplicateValues" dxfId="22" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="380"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F136">
-    <cfRule type="duplicateValues" dxfId="21" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="377"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="20" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="316"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F137:F1048576 F62 F7:F19">
-    <cfRule type="duplicateValues" dxfId="19" priority="2214"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2215"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2216"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="2217"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y33 Y62:Y137">
-    <cfRule type="containsText" dxfId="15" priority="224" operator="containsText" text="null">
-      <formula>NOT(ISERROR(SEARCH("null",Y7)))</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F137 F62 F7:F19 F142:F1048576">
+    <cfRule type="duplicateValues" dxfId="31" priority="2225"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="2226"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2227"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2228"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R34:R61">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:R87">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R88:R93">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y33 Y62:Y137">
+    <cfRule type="containsText" dxfId="19" priority="235" operator="containsText" text="null">
+      <formula>NOT(ISERROR(SEARCH("null",Y7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B138:B141">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F138:F141">
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q138:Q141">
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R138:R141">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P139:P141">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -17861,15 +18457,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -17934,7 +18530,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -18001,7 +18597,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18017,15 +18613,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -18048,7 +18644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -18077,22 +18673,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18104,28 +18700,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.69140625" customWidth="1"/>
-    <col min="5" max="5" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.3828125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.61328125" customWidth="1"/>
-    <col min="10" max="10" width="3.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.765625" customWidth="1"/>
-    <col min="12" max="12" width="6.61328125" customWidth="1"/>
-    <col min="13" max="13" width="21.3828125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.69140625" customWidth="1"/>
-    <col min="15" max="15" width="5.61328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.7109375" customWidth="1"/>
+    <col min="15" max="15" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -18178,7 +18774,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -18231,7 +18827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -18284,7 +18880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -18337,7 +18933,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -18390,7 +18986,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -18443,7 +19039,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -18496,7 +19092,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -18549,7 +19145,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -18602,7 +19198,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>10</v>
       </c>
@@ -18655,7 +19251,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>11</v>
       </c>

--- a/Versão5/SIS/Ontologia_Eletrica.xlsx
+++ b/Versão5/SIS/Ontologia_Eletrica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B39F2E-53E6-4A29-B4E6-5D094920F07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E16989-2606-419C-A538-7AB97C1C6506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -4513,14 +4513,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>43</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>47</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>48</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>49</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>53</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>54</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>56</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>60</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>62</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>63</v>
       </c>
@@ -4698,7 +4698,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -4709,19 +4709,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46260.466337731479</v>
+        <v>46264.570291203701</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>66</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>68</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>69</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>70</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>71</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -4797,38 +4797,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC147"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="60" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="60" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="60" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.69140625" style="60" customWidth="1"/>
+    <col min="4" max="4" width="9.53515625" style="60" customWidth="1"/>
+    <col min="5" max="5" width="10.53515625" style="60" customWidth="1"/>
     <col min="6" max="6" width="16" style="66" customWidth="1"/>
-    <col min="7" max="11" width="7.28515625" style="60" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="72.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="73.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="66.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.28515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="34.7109375" style="60" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="60" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="30" max="98" width="2.5703125" style="60" customWidth="1"/>
-    <col min="99" max="16384" width="9.140625" style="60"/>
+    <col min="7" max="11" width="7.3046875" style="60" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="72.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="66.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.15234375" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.53515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.3046875" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.69140625" style="60" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.84375" style="67" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" style="60" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="30" max="98" width="2.53515625" style="60" customWidth="1"/>
+    <col min="99" max="16384" width="9.15234375" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="43.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="43.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>90</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>2</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>3</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>4</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>5</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>6</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>7</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>8</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="58">
         <v>9</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="58">
         <v>10</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="58">
         <v>11</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="58">
         <v>12</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="58">
         <v>13</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="58">
         <v>14</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="58">
         <v>15</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="58">
         <v>16</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="58">
         <v>17</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="58">
         <v>18</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="58">
         <v>19</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="58">
         <v>20</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="58">
         <v>21</v>
       </c>
@@ -6839,7 +6839,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="58">
         <v>22</v>
       </c>
@@ -6936,7 +6936,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="58">
         <v>23</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="58">
         <v>24</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="58">
         <v>25</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="58">
         <v>26</v>
       </c>
@@ -7324,7 +7324,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="58">
         <v>27</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="58">
         <v>28</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="58">
         <v>29</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="58">
         <v>30</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="58">
         <v>31</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="58">
         <v>32</v>
       </c>
@@ -7906,7 +7906,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="58">
         <v>33</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="58">
         <v>34</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="58">
         <v>35</v>
       </c>
@@ -8197,7 +8197,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="58">
         <v>36</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="58">
         <v>37</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="58">
         <v>38</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="58">
         <v>39</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="58">
         <v>40</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="41" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="58">
         <v>41</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="58">
         <v>42</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="58">
         <v>43</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="58">
         <v>44</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="58">
         <v>45</v>
       </c>
@@ -9167,7 +9167,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="58">
         <v>46</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="58">
         <v>47</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="58">
         <v>48</v>
       </c>
@@ -9458,7 +9458,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="58">
         <v>49</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="58">
         <v>50</v>
       </c>
@@ -9652,7 +9652,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="58">
         <v>51</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="58">
         <v>52</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="58">
         <v>53</v>
       </c>
@@ -9943,7 +9943,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="58">
         <v>54</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="55" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="58">
         <v>55</v>
       </c>
@@ -10137,7 +10137,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="56" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="58">
         <v>56</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="57" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="58">
         <v>57</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="58" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="58">
         <v>58</v>
       </c>
@@ -10428,7 +10428,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="59" spans="1:29" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="58">
         <v>59</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="58">
         <v>60</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="58">
         <v>61</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="58">
         <v>62</v>
       </c>
@@ -10815,7 +10815,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="58">
         <v>63</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="58">
         <v>64</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="58">
         <v>65</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="58">
         <v>66</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="58">
         <v>67</v>
       </c>
@@ -11295,7 +11295,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="58">
         <v>68</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="58">
         <v>69</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="58">
         <v>70</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="58">
         <v>71</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="58">
         <v>72</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="58">
         <v>73</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="58">
         <v>74</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="58">
         <v>75</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="58">
         <v>76</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="58">
         <v>77</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="58">
         <v>78</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="58">
         <v>79</v>
       </c>
@@ -12447,7 +12447,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="58">
         <v>80</v>
       </c>
@@ -12543,7 +12543,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="58">
         <v>81</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="58">
         <v>82</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="58">
         <v>83</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="58">
         <v>84</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="58">
         <v>85</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="58">
         <v>86</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="58">
         <v>87</v>
       </c>
@@ -13215,7 +13215,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="58">
         <v>88</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="58">
         <v>89</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="58">
         <v>90</v>
       </c>
@@ -13506,7 +13506,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="58">
         <v>91</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="58">
         <v>92</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="58">
         <v>93</v>
       </c>
@@ -13797,7 +13797,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="58">
         <v>94</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="58">
         <v>95</v>
       </c>
@@ -13989,7 +13989,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="58">
         <v>96</v>
       </c>
@@ -14085,7 +14085,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="58">
         <v>97</v>
       </c>
@@ -14181,7 +14181,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="58">
         <v>98</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="58">
         <v>99</v>
       </c>
@@ -14373,7 +14373,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="58">
         <v>100</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="58">
         <v>101</v>
       </c>
@@ -14565,7 +14565,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="58">
         <v>102</v>
       </c>
@@ -14661,7 +14661,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="58">
         <v>103</v>
       </c>
@@ -14758,7 +14758,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="58">
         <v>104</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="58">
         <v>105</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="58">
         <v>106</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="58">
         <v>107</v>
       </c>
@@ -15146,7 +15146,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="58">
         <v>108</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="58">
         <v>109</v>
       </c>
@@ -15340,7 +15340,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="58">
         <v>110</v>
       </c>
@@ -15437,7 +15437,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="58">
         <v>111</v>
       </c>
@@ -15534,7 +15534,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="58">
         <v>112</v>
       </c>
@@ -15631,7 +15631,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="58">
         <v>113</v>
       </c>
@@ -15728,7 +15728,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="114" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="58">
         <v>114</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="115" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="58">
         <v>115</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="116" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="58">
         <v>116</v>
       </c>
@@ -16019,7 +16019,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="117" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="58">
         <v>117</v>
       </c>
@@ -16116,7 +16116,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="118" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="58">
         <v>118</v>
       </c>
@@ -16213,7 +16213,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="119" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="58">
         <v>119</v>
       </c>
@@ -16310,7 +16310,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="120" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="58">
         <v>120</v>
       </c>
@@ -16407,7 +16407,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="121" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="58">
         <v>121</v>
       </c>
@@ -16504,7 +16504,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="122" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="58">
         <v>122</v>
       </c>
@@ -16601,7 +16601,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="123" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="58">
         <v>123</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="124" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="58">
         <v>124</v>
       </c>
@@ -16795,7 +16795,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="125" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="58">
         <v>125</v>
       </c>
@@ -16892,7 +16892,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="126" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="58">
         <v>126</v>
       </c>
@@ -16989,7 +16989,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="127" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="58">
         <v>127</v>
       </c>
@@ -17086,7 +17086,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="128" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="58">
         <v>128</v>
       </c>
@@ -17183,7 +17183,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="129" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="58">
         <v>129</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="130" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="58">
         <v>130</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="131" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="58">
         <v>131</v>
       </c>
@@ -17474,7 +17474,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="132" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="58">
         <v>132</v>
       </c>
@@ -17571,7 +17571,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="133" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="58">
         <v>133</v>
       </c>
@@ -17668,7 +17668,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="134" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="58">
         <v>134</v>
       </c>
@@ -17765,7 +17765,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="135" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="58">
         <v>135</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="136" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="58">
         <v>136</v>
       </c>
@@ -17959,7 +17959,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="137" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="58">
         <v>137</v>
       </c>
@@ -18056,7 +18056,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="138" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="58">
         <v>138</v>
       </c>
@@ -18067,10 +18067,10 @@
         <v>782</v>
       </c>
       <c r="D138" s="63" t="s">
+        <v>784</v>
+      </c>
+      <c r="E138" s="63" t="s">
         <v>783</v>
-      </c>
-      <c r="E138" s="63" t="s">
-        <v>784</v>
       </c>
       <c r="F138" s="63" t="s">
         <v>785</v>
@@ -18096,11 +18096,11 @@
       </c>
       <c r="M138" s="34" t="str">
         <f t="shared" si="48"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N138" s="34" t="str">
         <f t="shared" si="48"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O138" s="34" t="str">
         <f t="shared" si="48"/>
@@ -18126,11 +18126,11 @@
       </c>
       <c r="U138" s="30" t="str">
         <f t="shared" si="51"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V138" s="69" t="str">
         <f t="shared" si="51"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W138" s="30" t="s">
         <v>108</v>
@@ -18155,7 +18155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="58">
         <v>139</v>
       </c>
@@ -18254,7 +18254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="58">
         <v>140</v>
       </c>
@@ -18353,7 +18353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="58">
         <v>141</v>
       </c>
@@ -18452,7 +18452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="58">
         <v>142</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="58">
         <v>143</v>
       </c>
@@ -18650,7 +18650,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="58">
         <v>144</v>
       </c>
@@ -18749,7 +18749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="58">
         <v>145</v>
       </c>
@@ -18848,7 +18848,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="58">
         <v>146</v>
       </c>
@@ -18947,7 +18947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="58">
         <v>147</v>
       </c>
@@ -19222,15 +19222,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -19295,7 +19295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -19378,15 +19378,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -19409,7 +19409,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -19465,36 +19465,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:AI18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" customWidth="1"/>
+    <col min="3" max="3" width="9.84375" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" customWidth="1"/>
-    <col min="7" max="7" width="36.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.53515625" customWidth="1"/>
+    <col min="6" max="6" width="5.3046875" customWidth="1"/>
+    <col min="7" max="7" width="36.69140625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" customWidth="1"/>
+    <col min="9" max="9" width="6.69140625" customWidth="1"/>
+    <col min="10" max="10" width="7.3828125" customWidth="1"/>
+    <col min="11" max="11" width="10.3046875" customWidth="1"/>
+    <col min="12" max="12" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.3046875" customWidth="1"/>
+    <col min="14" max="14" width="6.69140625" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" customWidth="1"/>
-    <col min="17" max="17" width="6.28515625" customWidth="1"/>
-    <col min="18" max="19" width="5.7109375" customWidth="1"/>
+    <col min="16" max="16" width="4.84375" customWidth="1"/>
+    <col min="17" max="17" width="6.3046875" customWidth="1"/>
+    <col min="18" max="19" width="5.69140625" customWidth="1"/>
     <col min="20" max="20" width="3" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="4.7109375" customWidth="1"/>
-    <col min="23" max="23" width="11.7109375" customWidth="1"/>
-    <col min="24" max="24" width="6.85546875" customWidth="1"/>
-    <col min="25" max="25" width="7.85546875" customWidth="1"/>
-    <col min="26" max="35" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.69140625" customWidth="1"/>
+    <col min="23" max="23" width="11.69140625" customWidth="1"/>
+    <col min="24" max="24" width="6.84375" customWidth="1"/>
+    <col min="25" max="25" width="7.84375" customWidth="1"/>
+    <col min="26" max="35" width="2.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>4</v>
       </c>
@@ -20029,7 +20029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>5</v>
       </c>
@@ -20136,7 +20136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>6</v>
       </c>
@@ -20243,7 +20243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>7</v>
       </c>
@@ -20350,7 +20350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>8</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>9</v>
       </c>
@@ -20564,7 +20564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>10</v>
       </c>
@@ -20671,7 +20671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>11</v>
       </c>
@@ -20778,7 +20778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>12</v>
       </c>
@@ -20885,7 +20885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>13</v>
       </c>
@@ -20993,7 +20993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>14</v>
       </c>
@@ -21101,7 +21101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>15</v>
       </c>
@@ -21209,7 +21209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>16</v>
       </c>
@@ -21317,7 +21317,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>17</v>
       </c>

--- a/Versão5/SIS/Ontologia_Eletrica.xlsx
+++ b/Versão5/SIS/Ontologia_Eletrica.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E16989-2606-419C-A538-7AB97C1C6506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7147B28-E88C-4EB7-A416-C804967ACB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3711" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3944" uniqueCount="879">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2429,12 +2429,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
     <t>De.Elétrica</t>
   </si>
   <si>
@@ -2646,6 +2640,75 @@
   </si>
   <si>
     <t>Tug_111233</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>Circuito distribuidor de unidade residencial.</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2736,7 +2799,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2893,6 +2956,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -3006,7 +3075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3241,11 +3310,14 @@
     <xf numFmtId="0" fontId="4" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="85">
+  <dxfs count="87">
     <dxf>
       <font>
         <b val="0"/>
@@ -3501,6 +3573,26 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4513,14 +4605,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>43</v>
       </c>
@@ -4531,7 +4623,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
@@ -4542,7 +4634,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>47</v>
       </c>
@@ -4553,7 +4645,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>48</v>
       </c>
@@ -4564,7 +4656,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>49</v>
       </c>
@@ -4576,7 +4668,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -4588,7 +4680,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
@@ -4599,7 +4691,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>53</v>
       </c>
@@ -4610,7 +4702,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>54</v>
       </c>
@@ -4621,7 +4713,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>56</v>
       </c>
@@ -4632,7 +4724,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -4643,7 +4735,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>59</v>
       </c>
@@ -4654,7 +4746,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>60</v>
       </c>
@@ -4665,7 +4757,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>61</v>
       </c>
@@ -4676,7 +4768,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>62</v>
       </c>
@@ -4687,7 +4779,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>63</v>
       </c>
@@ -4698,7 +4790,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>64</v>
       </c>
@@ -4709,19 +4801,19 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46264.570291203701</v>
+        <v>46268.700793750002</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>66</v>
       </c>
@@ -4732,7 +4824,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>68</v>
       </c>
@@ -4743,7 +4835,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>69</v>
       </c>
@@ -4754,7 +4846,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>70</v>
       </c>
@@ -4765,7 +4857,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>71</v>
       </c>
@@ -4776,7 +4868,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>85</v>
       </c>
@@ -4796,39 +4888,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC147"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD151"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" style="60" customWidth="1"/>
-    <col min="4" max="4" width="9.53515625" style="60" customWidth="1"/>
-    <col min="5" max="5" width="10.53515625" style="60" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="60" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="60" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="60" customWidth="1"/>
     <col min="6" max="6" width="16" style="66" customWidth="1"/>
-    <col min="7" max="11" width="7.3046875" style="60" customWidth="1"/>
-    <col min="12" max="12" width="8.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.53515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.84375" style="60" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="72.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="73.53515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="66.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.15234375" style="60" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.53515625" style="60" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.3046875" style="60" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="34.69140625" style="60" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.84375" style="67" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" style="60" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="30" max="98" width="2.53515625" style="60" customWidth="1"/>
-    <col min="99" max="16384" width="9.15234375" style="60"/>
+    <col min="7" max="11" width="7.28515625" style="60" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="72.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="66.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="60" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.28515625" style="60" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="34.7109375" style="60" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="30.7109375" style="67" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="60" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="3.7109375" style="60" customWidth="1"/>
+    <col min="31" max="98" width="2.5703125" style="60" customWidth="1"/>
+    <col min="99" max="16384" width="9.140625" style="60"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="43.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="43.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>90</v>
       </c>
@@ -4916,8 +5009,11 @@
       <c r="AC1" s="35" t="s">
         <v>82</v>
       </c>
+      <c r="AD1" s="35" t="s">
+        <v>878</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="58">
         <v>2</v>
       </c>
@@ -5012,8 +5108,11 @@
       <c r="AC2" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD2" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58">
         <v>3</v>
       </c>
@@ -5108,8 +5207,11 @@
       <c r="AC3" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD3" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="58">
         <v>4</v>
       </c>
@@ -5204,8 +5306,11 @@
       <c r="AC4" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD4" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="58">
         <v>5</v>
       </c>
@@ -5300,8 +5405,11 @@
       <c r="AC5" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD5" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="58">
         <v>6</v>
       </c>
@@ -5396,8 +5504,11 @@
       <c r="AC6" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD6" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="58">
         <v>7</v>
       </c>
@@ -5492,8 +5603,11 @@
       <c r="AC7" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD7" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58">
         <v>8</v>
       </c>
@@ -5588,8 +5702,11 @@
       <c r="AC8" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD8" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58">
         <v>9</v>
       </c>
@@ -5684,8 +5801,11 @@
       <c r="AC9" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD9" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="58">
         <v>10</v>
       </c>
@@ -5780,8 +5900,11 @@
       <c r="AC10" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD10" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>11</v>
       </c>
@@ -5876,8 +5999,11 @@
       <c r="AC11" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD11" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="58">
         <v>12</v>
       </c>
@@ -5972,8 +6098,11 @@
       <c r="AC12" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD12" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>13</v>
       </c>
@@ -6068,8 +6197,11 @@
       <c r="AC13" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD13" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="58">
         <v>14</v>
       </c>
@@ -6164,8 +6296,11 @@
       <c r="AC14" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD14" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>15</v>
       </c>
@@ -6260,8 +6395,11 @@
       <c r="AC15" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD15" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="58">
         <v>16</v>
       </c>
@@ -6356,8 +6494,11 @@
       <c r="AC16" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD16" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="58">
         <v>17</v>
       </c>
@@ -6452,8 +6593,11 @@
       <c r="AC17" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD17" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58">
         <v>18</v>
       </c>
@@ -6548,8 +6692,11 @@
       <c r="AC18" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD18" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>19</v>
       </c>
@@ -6644,8 +6791,11 @@
       <c r="AC19" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD19" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>20</v>
       </c>
@@ -6741,8 +6891,11 @@
       <c r="AC20" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD20" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="58">
         <v>21</v>
       </c>
@@ -6838,8 +6991,11 @@
       <c r="AC21" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD21" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
         <v>22</v>
       </c>
@@ -6935,8 +7091,11 @@
       <c r="AC22" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD22" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="58">
         <v>23</v>
       </c>
@@ -7032,8 +7191,11 @@
       <c r="AC23" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD23" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>24</v>
       </c>
@@ -7129,8 +7291,11 @@
       <c r="AC24" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD24" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="58">
         <v>25</v>
       </c>
@@ -7226,8 +7391,11 @@
       <c r="AC25" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD25" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="58">
         <v>26</v>
       </c>
@@ -7323,8 +7491,11 @@
       <c r="AC26" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD26" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="58">
         <v>27</v>
       </c>
@@ -7420,8 +7591,11 @@
       <c r="AC27" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD27" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="58">
         <v>28</v>
       </c>
@@ -7517,8 +7691,11 @@
       <c r="AC28" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD28" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="58">
         <v>29</v>
       </c>
@@ -7614,8 +7791,11 @@
       <c r="AC29" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD29" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="58">
         <v>30</v>
       </c>
@@ -7711,8 +7891,11 @@
       <c r="AC30" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD30" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
         <v>31</v>
       </c>
@@ -7808,8 +7991,11 @@
       <c r="AC31" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD31" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="58">
         <v>32</v>
       </c>
@@ -7905,8 +8091,11 @@
       <c r="AC32" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD32" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>33</v>
       </c>
@@ -8002,8 +8191,11 @@
       <c r="AC33" s="30" t="s">
         <v>667</v>
       </c>
+      <c r="AD33" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="58">
         <v>34</v>
       </c>
@@ -8099,8 +8291,11 @@
       <c r="AC34" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD34" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>35</v>
       </c>
@@ -8196,8 +8391,11 @@
       <c r="AC35" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD35" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>36</v>
       </c>
@@ -8293,8 +8491,11 @@
       <c r="AC36" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD36" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58">
         <v>37</v>
       </c>
@@ -8390,8 +8591,11 @@
       <c r="AC37" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD37" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
         <v>38</v>
       </c>
@@ -8487,8 +8691,11 @@
       <c r="AC38" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD38" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>39</v>
       </c>
@@ -8584,8 +8791,11 @@
       <c r="AC39" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD39" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="58">
         <v>40</v>
       </c>
@@ -8681,8 +8891,11 @@
       <c r="AC40" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD40" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="58">
         <v>41</v>
       </c>
@@ -8778,8 +8991,11 @@
       <c r="AC41" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD41" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="58">
         <v>42</v>
       </c>
@@ -8875,8 +9091,11 @@
       <c r="AC42" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD42" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>43</v>
       </c>
@@ -8972,8 +9191,11 @@
       <c r="AC43" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD43" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="58">
         <v>44</v>
       </c>
@@ -9069,8 +9291,11 @@
       <c r="AC44" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD44" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="58">
         <v>45</v>
       </c>
@@ -9166,8 +9391,11 @@
       <c r="AC45" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD45" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="58">
         <v>46</v>
       </c>
@@ -9263,8 +9491,11 @@
       <c r="AC46" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD46" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
         <v>47</v>
       </c>
@@ -9360,8 +9591,11 @@
       <c r="AC47" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD47" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="58">
         <v>48</v>
       </c>
@@ -9457,8 +9691,11 @@
       <c r="AC48" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD48" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="58">
         <v>49</v>
       </c>
@@ -9554,8 +9791,11 @@
       <c r="AC49" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD49" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
         <v>50</v>
       </c>
@@ -9651,8 +9891,11 @@
       <c r="AC50" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD50" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58">
         <v>51</v>
       </c>
@@ -9748,8 +9991,11 @@
       <c r="AC51" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD51" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="58">
         <v>52</v>
       </c>
@@ -9845,8 +10091,11 @@
       <c r="AC52" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD52" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="58">
         <v>53</v>
       </c>
@@ -9942,8 +10191,11 @@
       <c r="AC53" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD53" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="58">
         <v>54</v>
       </c>
@@ -10039,8 +10291,11 @@
       <c r="AC54" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD54" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="58">
         <v>55</v>
       </c>
@@ -10136,8 +10391,11 @@
       <c r="AC55" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD55" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="58">
         <v>56</v>
       </c>
@@ -10233,8 +10491,11 @@
       <c r="AC56" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD56" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="58">
         <v>57</v>
       </c>
@@ -10330,8 +10591,11 @@
       <c r="AC57" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD57" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="58">
         <v>58</v>
       </c>
@@ -10427,8 +10691,11 @@
       <c r="AC58" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD58" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" s="65" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" s="65" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="58">
         <v>59</v>
       </c>
@@ -10524,8 +10791,11 @@
       <c r="AC59" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD59" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="58">
         <v>60</v>
       </c>
@@ -10621,8 +10891,11 @@
       <c r="AC60" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD60" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="58">
         <v>61</v>
       </c>
@@ -10718,8 +10991,11 @@
       <c r="AC61" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD61" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="58">
         <v>62</v>
       </c>
@@ -10814,8 +11090,11 @@
       <c r="AC62" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD62" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="58">
         <v>63</v>
       </c>
@@ -10910,8 +11189,11 @@
       <c r="AC63" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD63" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
         <v>64</v>
       </c>
@@ -11006,8 +11288,11 @@
       <c r="AC64" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD64" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="58">
         <v>65</v>
       </c>
@@ -11102,8 +11387,11 @@
       <c r="AC65" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD65" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="58">
         <v>66</v>
       </c>
@@ -11198,8 +11486,11 @@
       <c r="AC66" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD66" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="58">
         <v>67</v>
       </c>
@@ -11294,8 +11585,11 @@
       <c r="AC67" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD67" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
         <v>68</v>
       </c>
@@ -11390,8 +11684,11 @@
       <c r="AC68" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD68" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="58">
         <v>69</v>
       </c>
@@ -11486,8 +11783,11 @@
       <c r="AC69" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD69" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
         <v>70</v>
       </c>
@@ -11582,8 +11882,11 @@
       <c r="AC70" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD70" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="58">
         <v>71</v>
       </c>
@@ -11678,8 +11981,11 @@
       <c r="AC71" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD71" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="58">
         <v>72</v>
       </c>
@@ -11774,8 +12080,11 @@
       <c r="AC72" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD72" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="58">
         <v>73</v>
       </c>
@@ -11870,8 +12179,11 @@
       <c r="AC73" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD73" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
         <v>74</v>
       </c>
@@ -11966,8 +12278,11 @@
       <c r="AC74" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD74" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="58">
         <v>75</v>
       </c>
@@ -12062,8 +12377,11 @@
       <c r="AC75" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD75" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="58">
         <v>76</v>
       </c>
@@ -12158,8 +12476,11 @@
       <c r="AC76" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD76" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
         <v>77</v>
       </c>
@@ -12254,8 +12575,11 @@
       <c r="AC77" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD77" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="58">
         <v>78</v>
       </c>
@@ -12350,8 +12674,11 @@
       <c r="AC78" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD78" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="58">
         <v>79</v>
       </c>
@@ -12446,8 +12773,11 @@
       <c r="AC79" s="30" t="s">
         <v>666</v>
       </c>
+      <c r="AD79" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
         <v>80</v>
       </c>
@@ -12542,8 +12872,11 @@
       <c r="AC80" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD80" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="58">
         <v>81</v>
       </c>
@@ -12638,8 +12971,11 @@
       <c r="AC81" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD81" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="58">
         <v>82</v>
       </c>
@@ -12734,8 +13070,11 @@
       <c r="AC82" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD82" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
         <v>83</v>
       </c>
@@ -12830,8 +13169,11 @@
       <c r="AC83" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD83" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
         <v>84</v>
       </c>
@@ -12926,8 +13268,11 @@
       <c r="AC84" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD84" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="58">
         <v>85</v>
       </c>
@@ -13022,8 +13367,11 @@
       <c r="AC85" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD85" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="58">
         <v>86</v>
       </c>
@@ -13118,8 +13466,11 @@
       <c r="AC86" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD86" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" ht="6.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:30" ht="6.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="58">
         <v>87</v>
       </c>
@@ -13214,8 +13565,11 @@
       <c r="AC87" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD87" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="58">
         <v>88</v>
       </c>
@@ -13311,8 +13665,11 @@
       <c r="AC88" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD88" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="58">
         <v>89</v>
       </c>
@@ -13408,8 +13765,11 @@
       <c r="AC89" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD89" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="58">
         <v>90</v>
       </c>
@@ -13505,8 +13865,11 @@
       <c r="AC90" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD90" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="58">
         <v>91</v>
       </c>
@@ -13602,8 +13965,11 @@
       <c r="AC91" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD91" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="58">
         <v>92</v>
       </c>
@@ -13699,8 +14065,11 @@
       <c r="AC92" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD92" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="58">
         <v>93</v>
       </c>
@@ -13796,8 +14165,11 @@
       <c r="AC93" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD93" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="58">
         <v>94</v>
       </c>
@@ -13892,8 +14264,11 @@
       <c r="AC94" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD94" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="58">
         <v>95</v>
       </c>
@@ -13988,8 +14363,11 @@
       <c r="AC95" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD95" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
         <v>96</v>
       </c>
@@ -14084,8 +14462,11 @@
       <c r="AC96" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD96" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="58">
         <v>97</v>
       </c>
@@ -14180,8 +14561,11 @@
       <c r="AC97" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD97" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
         <v>98</v>
       </c>
@@ -14276,8 +14660,11 @@
       <c r="AC98" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD98" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="58">
         <v>99</v>
       </c>
@@ -14372,8 +14759,11 @@
       <c r="AC99" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD99" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="58">
         <v>100</v>
       </c>
@@ -14468,8 +14858,11 @@
       <c r="AC100" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD100" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="58">
         <v>101</v>
       </c>
@@ -14564,8 +14957,11 @@
       <c r="AC101" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD101" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="102" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="58">
         <v>102</v>
       </c>
@@ -14660,8 +15056,11 @@
       <c r="AC102" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD102" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="103" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="58">
         <v>103</v>
       </c>
@@ -14757,8 +15156,11 @@
       <c r="AC103" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD103" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="104" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
         <v>104</v>
       </c>
@@ -14854,8 +15256,11 @@
       <c r="AC104" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD104" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="105" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="58">
         <v>105</v>
       </c>
@@ -14951,8 +15356,11 @@
       <c r="AC105" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD105" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="106" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="58">
         <v>106</v>
       </c>
@@ -15048,8 +15456,11 @@
       <c r="AC106" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD106" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="107" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="58">
         <v>107</v>
       </c>
@@ -15145,8 +15556,11 @@
       <c r="AC107" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD107" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="108" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="58">
         <v>108</v>
       </c>
@@ -15242,8 +15656,11 @@
       <c r="AC108" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD108" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="109" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
         <v>109</v>
       </c>
@@ -15339,8 +15756,11 @@
       <c r="AC109" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD109" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="110" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="58">
         <v>110</v>
       </c>
@@ -15436,8 +15856,11 @@
       <c r="AC110" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD110" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="111" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="58">
         <v>111</v>
       </c>
@@ -15533,8 +15956,11 @@
       <c r="AC111" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD111" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="112" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="58">
         <v>112</v>
       </c>
@@ -15630,8 +16056,11 @@
       <c r="AC112" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD112" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="113" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
         <v>113</v>
       </c>
@@ -15727,8 +16156,11 @@
       <c r="AC113" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD113" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="114" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
         <v>114</v>
       </c>
@@ -15824,8 +16256,11 @@
       <c r="AC114" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD114" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="115" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="58">
         <v>115</v>
       </c>
@@ -15921,8 +16356,11 @@
       <c r="AC115" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD115" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="116" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="58">
         <v>116</v>
       </c>
@@ -16018,8 +16456,11 @@
       <c r="AC116" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD116" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="117" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
         <v>117</v>
       </c>
@@ -16115,8 +16556,11 @@
       <c r="AC117" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD117" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="118" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
         <v>118</v>
       </c>
@@ -16212,8 +16656,11 @@
       <c r="AC118" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD118" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="119" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="58">
         <v>119</v>
       </c>
@@ -16309,8 +16756,11 @@
       <c r="AC119" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD119" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="120" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="58">
         <v>120</v>
       </c>
@@ -16406,8 +16856,11 @@
       <c r="AC120" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD120" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="121" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
         <v>121</v>
       </c>
@@ -16503,8 +16956,11 @@
       <c r="AC121" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD121" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="122" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="58">
         <v>122</v>
       </c>
@@ -16600,8 +17056,11 @@
       <c r="AC122" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD122" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="123" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="58">
         <v>123</v>
       </c>
@@ -16697,8 +17156,11 @@
       <c r="AC123" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD123" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="124" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="58">
         <v>124</v>
       </c>
@@ -16794,8 +17256,11 @@
       <c r="AC124" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD124" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="125" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="58">
         <v>125</v>
       </c>
@@ -16891,8 +17356,11 @@
       <c r="AC125" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD125" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="126" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="58">
         <v>126</v>
       </c>
@@ -16988,8 +17456,11 @@
       <c r="AC126" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD126" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="127" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
         <v>127</v>
       </c>
@@ -17085,8 +17556,11 @@
       <c r="AC127" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD127" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="128" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
         <v>128</v>
       </c>
@@ -17182,8 +17656,11 @@
       <c r="AC128" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD128" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="129" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="58">
         <v>129</v>
       </c>
@@ -17279,8 +17756,11 @@
       <c r="AC129" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD129" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="130" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
         <v>130</v>
       </c>
@@ -17358,7 +17838,7 @@
         <v>108</v>
       </c>
       <c r="X130" s="59" t="str">
-        <f t="shared" ref="X130:X138" si="45">CONCATENATE("Key-ELET-",A130)</f>
+        <f t="shared" ref="X130:X137" si="45">CONCATENATE("Key-ELET-",A130)</f>
         <v>Key-ELET-130</v>
       </c>
       <c r="Y130" s="30" t="s">
@@ -17376,8 +17856,11 @@
       <c r="AC130" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD130" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="131" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="58">
         <v>131</v>
       </c>
@@ -17473,8 +17956,11 @@
       <c r="AC131" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD131" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="132" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="58">
         <v>132</v>
       </c>
@@ -17570,8 +18056,11 @@
       <c r="AC132" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD132" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="133" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="58">
         <v>133</v>
       </c>
@@ -17667,8 +18156,11 @@
       <c r="AC133" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD133" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="134" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="58">
         <v>134</v>
       </c>
@@ -17764,8 +18256,11 @@
       <c r="AC134" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD134" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="135" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
         <v>135</v>
       </c>
@@ -17861,8 +18356,11 @@
       <c r="AC135" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD135" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="136" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="58">
         <v>136</v>
       </c>
@@ -17958,8 +18456,11 @@
       <c r="AC136" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD136" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="137" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="58">
         <v>137</v>
       </c>
@@ -18055,8 +18556,11 @@
       <c r="AC137" s="30" t="s">
         <v>665</v>
       </c>
+      <c r="AD137" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="138" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="58">
         <v>138</v>
       </c>
@@ -18064,16 +18568,16 @@
         <v>781</v>
       </c>
       <c r="C138" s="63" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D138" s="63" t="s">
-        <v>784</v>
+        <v>840</v>
       </c>
       <c r="E138" s="63" t="s">
-        <v>783</v>
+        <v>843</v>
       </c>
       <c r="F138" s="63" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G138" s="62" t="s">
         <v>9</v>
@@ -18091,62 +18595,62 @@
         <v>9</v>
       </c>
       <c r="L138" s="34" t="str">
-        <f t="shared" ref="L138:O138" si="48">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="L138" si="48">SUBSTITUTE(CONCATENATE("", C138), ".", " ")</f>
+        <v>De Elétrica</v>
       </c>
       <c r="M138" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v>Macros</v>
+        <f t="shared" ref="M138" si="49">SUBSTITUTE(CONCATENATE("", D138), ".", " ")</f>
+        <v>Tensões Elétricas</v>
       </c>
       <c r="N138" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v>Métodos</v>
+        <f t="shared" ref="N138" si="50">SUBSTITUTE(CONCATENATE("", E138), ".", " ")</f>
+        <v>Tensão Alta</v>
       </c>
       <c r="O138" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P138" s="30" t="s">
-        <v>786</v>
+        <f t="shared" ref="O138" si="51">SUBSTITUTE(CONCATENATE("", F138), ".", " ")</f>
+        <v>Elétrica AT</v>
+      </c>
+      <c r="P138" s="72" t="s">
+        <v>822</v>
       </c>
       <c r="Q138" s="68" t="str">
-        <f t="shared" ref="Q138" si="49">_xlfn.TRANSLATE(P138,"pt","es")</f>
-        <v>Aplicación Revit</v>
+        <f t="shared" ref="Q138" si="52">_xlfn.TRANSLATE(P138,"pt","es")</f>
+        <v>Instalación eléctrica de alta tensión (HV), con voltaje superior a 50 kV.</v>
       </c>
       <c r="R138" s="68" t="str">
-        <f t="shared" ref="R138" si="50">_xlfn.TRANSLATE(P138,"pt","en")</f>
-        <v>Revit App</v>
+        <f t="shared" ref="R138" si="53">_xlfn.TRANSLATE(P138,"pt","en")</f>
+        <v>High voltage (HV) electrical installation, with voltage above 50 kV.</v>
       </c>
       <c r="S138" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T138" s="30" t="str">
-        <f t="shared" ref="T138:V138" si="51">SUBSTITUTE(C138, ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="T138" si="54">SUBSTITUTE(C138, ".", " ")</f>
+        <v>De Elétrica</v>
       </c>
       <c r="U138" s="30" t="str">
-        <f t="shared" si="51"/>
-        <v>Macros</v>
+        <f t="shared" ref="U138" si="55">SUBSTITUTE(D138, ".", " ")</f>
+        <v>Tensões Elétricas</v>
       </c>
       <c r="V138" s="69" t="str">
-        <f t="shared" si="51"/>
-        <v>Métodos</v>
+        <f t="shared" ref="V138" si="56">SUBSTITUTE(E138, ".", " ")</f>
+        <v>Tensão Alta</v>
       </c>
       <c r="W138" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X138" s="59" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="X138" si="57">CONCATENATE("Key-ELET-",A138)</f>
         <v>Key-ELET-138</v>
       </c>
-      <c r="Y138" s="70" t="s">
-        <v>9</v>
+      <c r="Y138" s="29" t="s">
+        <v>103</v>
       </c>
       <c r="Z138" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="AA138" s="70" t="s">
-        <v>9</v>
+      <c r="AA138" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="AB138" s="70" t="s">
         <v>9</v>
@@ -18154,8 +18658,11 @@
       <c r="AC138" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD138" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="139" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="58">
         <v>139</v>
       </c>
@@ -18163,13 +18670,13 @@
         <v>781</v>
       </c>
       <c r="C139" s="63" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D139" s="63" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E139" s="63" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F139" s="63" t="s">
         <v>788</v>
@@ -18190,52 +18697,52 @@
         <v>9</v>
       </c>
       <c r="L139" s="34" t="str">
-        <f t="shared" ref="L139" si="52">SUBSTITUTE(CONCATENATE("", C139), ".", " ")</f>
+        <f t="shared" ref="L139:L140" si="58">SUBSTITUTE(CONCATENATE("", C139), ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="M139" s="34" t="str">
-        <f t="shared" ref="M139" si="53">SUBSTITUTE(CONCATENATE("", D139), ".", " ")</f>
+        <f t="shared" ref="M139:M140" si="59">SUBSTITUTE(CONCATENATE("", D139), ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="N139" s="34" t="str">
-        <f t="shared" ref="N139" si="54">SUBSTITUTE(CONCATENATE("", E139), ".", " ")</f>
-        <v>Tensão Alta</v>
+        <f t="shared" ref="N139:N140" si="60">SUBSTITUTE(CONCATENATE("", E139), ".", " ")</f>
+        <v>Tensão Média</v>
       </c>
       <c r="O139" s="34" t="str">
-        <f t="shared" ref="O139" si="55">SUBSTITUTE(CONCATENATE("", F139), ".", " ")</f>
-        <v>Elétrica AT</v>
+        <f t="shared" ref="O139:O140" si="61">SUBSTITUTE(CONCATENATE("", F139), ".", " ")</f>
+        <v>Elétrica MT</v>
       </c>
       <c r="P139" s="72" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="Q139" s="68" t="str">
-        <f t="shared" ref="Q139" si="56">_xlfn.TRANSLATE(P139,"pt","es")</f>
-        <v>Instalación eléctrica de alta tensión (HV), con voltaje superior a 50 kV.</v>
+        <f t="shared" ref="Q139:Q140" si="62">_xlfn.TRANSLATE(P139,"pt","es")</f>
+        <v>Instalación eléctrica de media tensión (MV), con una tensión nominal generalmente entre 13,8 kV y 34,5 kV. Presente en la industria o en subestaciones.</v>
       </c>
       <c r="R139" s="68" t="str">
-        <f t="shared" ref="R139" si="57">_xlfn.TRANSLATE(P139,"pt","en")</f>
-        <v>High voltage (HV) electrical installation, with voltage above 50 kV.</v>
+        <f t="shared" ref="R139:R140" si="63">_xlfn.TRANSLATE(P139,"pt","en")</f>
+        <v>Medium voltage (MV) electrical installation, with a nominal voltage generally between 13.8 kV and 34.5 kV. Present in industry or substations.</v>
       </c>
       <c r="S139" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T139" s="30" t="str">
-        <f t="shared" ref="T139" si="58">SUBSTITUTE(C139, ".", " ")</f>
+        <f t="shared" ref="T139:T140" si="64">SUBSTITUTE(C139, ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="U139" s="30" t="str">
-        <f t="shared" ref="U139" si="59">SUBSTITUTE(D139, ".", " ")</f>
+        <f t="shared" ref="U139:U140" si="65">SUBSTITUTE(D139, ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="V139" s="69" t="str">
-        <f t="shared" ref="V139" si="60">SUBSTITUTE(E139, ".", " ")</f>
-        <v>Tensão Alta</v>
+        <f t="shared" ref="V139:V140" si="66">SUBSTITUTE(E139, ".", " ")</f>
+        <v>Tensão Média</v>
       </c>
       <c r="W139" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X139" s="59" t="str">
-        <f t="shared" ref="X139" si="61">CONCATENATE("Key-ELET-",A139)</f>
+        <f t="shared" ref="X139:X140" si="67">CONCATENATE("Key-ELET-",A139)</f>
         <v>Key-ELET-139</v>
       </c>
       <c r="Y139" s="29" t="s">
@@ -18253,8 +18760,11 @@
       <c r="AC139" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD139" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="140" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="58">
         <v>140</v>
       </c>
@@ -18262,17 +18772,17 @@
         <v>781</v>
       </c>
       <c r="C140" s="63" t="s">
+        <v>785</v>
+      </c>
+      <c r="D140" s="63" t="s">
+        <v>840</v>
+      </c>
+      <c r="E140" s="63" t="s">
+        <v>845</v>
+      </c>
+      <c r="F140" s="63" t="s">
         <v>787</v>
       </c>
-      <c r="D140" s="63" t="s">
-        <v>842</v>
-      </c>
-      <c r="E140" s="63" t="s">
-        <v>846</v>
-      </c>
-      <c r="F140" s="63" t="s">
-        <v>790</v>
-      </c>
       <c r="G140" s="62" t="s">
         <v>9</v>
       </c>
@@ -18289,52 +18799,52 @@
         <v>9</v>
       </c>
       <c r="L140" s="34" t="str">
-        <f t="shared" ref="L140:L141" si="62">SUBSTITUTE(CONCATENATE("", C140), ".", " ")</f>
+        <f t="shared" si="58"/>
         <v>De Elétrica</v>
       </c>
       <c r="M140" s="34" t="str">
-        <f t="shared" ref="M140:M141" si="63">SUBSTITUTE(CONCATENATE("", D140), ".", " ")</f>
+        <f t="shared" si="59"/>
         <v>Tensões Elétricas</v>
       </c>
       <c r="N140" s="34" t="str">
-        <f t="shared" ref="N140:N141" si="64">SUBSTITUTE(CONCATENATE("", E140), ".", " ")</f>
-        <v>Tensão Média</v>
+        <f t="shared" si="60"/>
+        <v>Tensão Baixa</v>
       </c>
       <c r="O140" s="34" t="str">
-        <f t="shared" ref="O140:O141" si="65">SUBSTITUTE(CONCATENATE("", F140), ".", " ")</f>
-        <v>Elétrica MT</v>
+        <f t="shared" si="61"/>
+        <v>Elétrica BT</v>
       </c>
       <c r="P140" s="72" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="Q140" s="68" t="str">
-        <f t="shared" ref="Q140:Q141" si="66">_xlfn.TRANSLATE(P140,"pt","es")</f>
-        <v>Instalación eléctrica de media tensión (MV), con una tensión nominal generalmente entre 13,8 kV y 34,5 kV. Presente en la industria o en subestaciones.</v>
+        <f t="shared" si="62"/>
+        <v>Instalación eléctrica de baja tensión (LV), con un voltaje nominal igual o inferior a 1 kV.</v>
       </c>
       <c r="R140" s="68" t="str">
-        <f t="shared" ref="R140:R141" si="67">_xlfn.TRANSLATE(P140,"pt","en")</f>
-        <v>Medium voltage (MV) electrical installation, with a nominal voltage usually between 13.8 kV and 34.5 kV. Present in industry or in substations.</v>
+        <f t="shared" si="63"/>
+        <v>Low voltage (LV) electrical installation, with a nominal voltage equal to or less than 1 kV.</v>
       </c>
       <c r="S140" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T140" s="30" t="str">
-        <f t="shared" ref="T140:T141" si="68">SUBSTITUTE(C140, ".", " ")</f>
+        <f t="shared" si="64"/>
         <v>De Elétrica</v>
       </c>
       <c r="U140" s="30" t="str">
-        <f t="shared" ref="U140:U141" si="69">SUBSTITUTE(D140, ".", " ")</f>
+        <f t="shared" si="65"/>
         <v>Tensões Elétricas</v>
       </c>
       <c r="V140" s="69" t="str">
-        <f t="shared" ref="V140:V141" si="70">SUBSTITUTE(E140, ".", " ")</f>
-        <v>Tensão Média</v>
+        <f t="shared" si="66"/>
+        <v>Tensão Baixa</v>
       </c>
       <c r="W140" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X140" s="59" t="str">
-        <f t="shared" ref="X140:X141" si="71">CONCATENATE("Key-ELET-",A140)</f>
+        <f t="shared" si="67"/>
         <v>Key-ELET-140</v>
       </c>
       <c r="Y140" s="29" t="s">
@@ -18352,8 +18862,11 @@
       <c r="AC140" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD140" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="141" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="58">
         <v>141</v>
       </c>
@@ -18361,16 +18874,16 @@
         <v>781</v>
       </c>
       <c r="C141" s="63" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D141" s="63" t="s">
+        <v>840</v>
+      </c>
+      <c r="E141" s="63" t="s">
         <v>842</v>
       </c>
-      <c r="E141" s="63" t="s">
-        <v>847</v>
-      </c>
       <c r="F141" s="63" t="s">
-        <v>789</v>
+        <v>846</v>
       </c>
       <c r="G141" s="62" t="s">
         <v>9</v>
@@ -18388,250 +18901,256 @@
         <v>9</v>
       </c>
       <c r="L141" s="34" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" ref="L141:L143" si="68">SUBSTITUTE(CONCATENATE("", C141), ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="M141" s="34" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="M141:M143" si="69">SUBSTITUTE(CONCATENATE("", D141), ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="N141" s="34" t="str">
-        <f t="shared" si="64"/>
-        <v>Tensão Baixa</v>
+        <f t="shared" ref="N141:N143" si="70">SUBSTITUTE(CONCATENATE("", E141), ".", " ")</f>
+        <v>Circuitos de Elétrica</v>
       </c>
       <c r="O141" s="34" t="str">
-        <f t="shared" si="65"/>
-        <v>Elétrica BT</v>
+        <f t="shared" ref="O141:O143" si="71">SUBSTITUTE(CONCATENATE("", F141), ".", " ")</f>
+        <v>Conexão de Entrada</v>
       </c>
       <c r="P141" s="72" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="Q141" s="68" t="str">
-        <f t="shared" si="66"/>
-        <v>Instalación eléctrica de baja tensión (LV), con un voltaje nominal igual o inferior a 1 kV.</v>
+        <f t="shared" ref="Q141:Q143" si="72">_xlfn.TRANSLATE(P141,"pt","es")</f>
+        <v>Circuito de entrada para la conexión a la red energética urbana.</v>
       </c>
       <c r="R141" s="68" t="str">
-        <f t="shared" si="67"/>
-        <v>Low voltage (LV) electrical installation, with a nominal voltage equal to or less than 1 kV.</v>
+        <f t="shared" ref="R141:R143" si="73">_xlfn.TRANSLATE(P141,"pt","en")</f>
+        <v>Input circuit for connection to the urban energy network.</v>
       </c>
       <c r="S141" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T141" s="30" t="str">
+        <f t="shared" ref="T141:T143" si="74">SUBSTITUTE(C141, ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="U141" s="30" t="str">
+        <f t="shared" ref="U141:U143" si="75">SUBSTITUTE(D141, ".", " ")</f>
+        <v>Tensões Elétricas</v>
+      </c>
+      <c r="V141" s="69" t="str">
+        <f t="shared" ref="V141:V143" si="76">SUBSTITUTE(E141, ".", " ")</f>
+        <v>Circuitos de Elétrica</v>
+      </c>
+      <c r="W141" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="X141" s="59" t="str">
+        <f t="shared" ref="X141:X143" si="77">CONCATENATE("Key-ELET-",A141)</f>
+        <v>Key-ELET-141</v>
+      </c>
+      <c r="Y141" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z141" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA141" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB141" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC141" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD141" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="58">
+        <v>142</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C142" s="63" t="s">
+        <v>785</v>
+      </c>
+      <c r="D142" s="63" t="s">
+        <v>840</v>
+      </c>
+      <c r="E142" s="63" t="s">
+        <v>842</v>
+      </c>
+      <c r="F142" s="63" t="s">
+        <v>825</v>
+      </c>
+      <c r="G142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K142" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L142" s="34" t="str">
+        <f t="shared" ref="L142" si="78">SUBSTITUTE(CONCATENATE("", C142), ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="M142" s="34" t="str">
+        <f t="shared" ref="M142" si="79">SUBSTITUTE(CONCATENATE("", D142), ".", " ")</f>
+        <v>Tensões Elétricas</v>
+      </c>
+      <c r="N142" s="34" t="str">
+        <f t="shared" ref="N142" si="80">SUBSTITUTE(CONCATENATE("", E142), ".", " ")</f>
+        <v>Circuitos de Elétrica</v>
+      </c>
+      <c r="O142" s="34" t="str">
+        <f t="shared" ref="O142" si="81">SUBSTITUTE(CONCATENATE("", F142), ".", " ")</f>
+        <v>Circuito Condomínio</v>
+      </c>
+      <c r="P142" s="72" t="s">
+        <v>827</v>
+      </c>
+      <c r="Q142" s="68" t="str">
+        <f t="shared" ref="Q142" si="82">_xlfn.TRANSLATE(P142,"pt","es")</f>
+        <v>Circuito distribuidor de condominios.</v>
+      </c>
+      <c r="R142" s="68" t="str">
+        <f t="shared" ref="R142" si="83">_xlfn.TRANSLATE(P142,"pt","en")</f>
+        <v>Condominium distributor circuit.</v>
+      </c>
+      <c r="S142" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T142" s="30" t="str">
+        <f t="shared" ref="T142" si="84">SUBSTITUTE(C142, ".", " ")</f>
+        <v>De Elétrica</v>
+      </c>
+      <c r="U142" s="30" t="str">
+        <f t="shared" ref="U142" si="85">SUBSTITUTE(D142, ".", " ")</f>
+        <v>Tensões Elétricas</v>
+      </c>
+      <c r="V142" s="69" t="str">
+        <f t="shared" ref="V142" si="86">SUBSTITUTE(E142, ".", " ")</f>
+        <v>Circuitos de Elétrica</v>
+      </c>
+      <c r="W142" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="X142" s="59" t="str">
+        <f t="shared" ref="X142" si="87">CONCATENATE("Key-ELET-",A142)</f>
+        <v>Key-ELET-142</v>
+      </c>
+      <c r="Y142" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z142" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA142" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB142" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC142" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD142" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="58">
+        <v>143</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C143" s="63" t="s">
+        <v>785</v>
+      </c>
+      <c r="D143" s="63" t="s">
+        <v>840</v>
+      </c>
+      <c r="E143" s="63" t="s">
+        <v>842</v>
+      </c>
+      <c r="F143" s="63" t="s">
+        <v>831</v>
+      </c>
+      <c r="G143" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H143" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I143" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J143" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K143" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L143" s="34" t="str">
         <f t="shared" si="68"/>
         <v>De Elétrica</v>
       </c>
-      <c r="U141" s="30" t="str">
+      <c r="M143" s="34" t="str">
         <f t="shared" si="69"/>
         <v>Tensões Elétricas</v>
       </c>
-      <c r="V141" s="69" t="str">
+      <c r="N143" s="34" t="str">
         <f t="shared" si="70"/>
-        <v>Tensão Baixa</v>
-      </c>
-      <c r="W141" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="X141" s="59" t="str">
+        <v>Circuitos de Elétrica</v>
+      </c>
+      <c r="O143" s="34" t="str">
         <f t="shared" si="71"/>
-        <v>Key-ELET-141</v>
-      </c>
-      <c r="Y141" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z141" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA141" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB141" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC141" s="70" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="58">
-        <v>142</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C142" s="63" t="s">
-        <v>787</v>
-      </c>
-      <c r="D142" s="63" t="s">
-        <v>842</v>
-      </c>
-      <c r="E142" s="63" t="s">
-        <v>844</v>
-      </c>
-      <c r="F142" s="63" t="s">
-        <v>848</v>
-      </c>
-      <c r="G142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K142" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L142" s="34" t="str">
-        <f t="shared" ref="L142:L144" si="72">SUBSTITUTE(CONCATENATE("", C142), ".", " ")</f>
+        <v>Circuito Unidade</v>
+      </c>
+      <c r="P143" s="72" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q143" s="68" t="str">
+        <f t="shared" si="72"/>
+        <v>Circuito distribuidor de la unidad residencial.</v>
+      </c>
+      <c r="R143" s="68" t="str">
+        <f t="shared" si="73"/>
+        <v>Residential unit distributor circuit.</v>
+      </c>
+      <c r="S143" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T143" s="30" t="str">
+        <f t="shared" si="74"/>
         <v>De Elétrica</v>
       </c>
-      <c r="M142" s="34" t="str">
-        <f t="shared" ref="M142:M144" si="73">SUBSTITUTE(CONCATENATE("", D142), ".", " ")</f>
+      <c r="U143" s="30" t="str">
+        <f t="shared" si="75"/>
         <v>Tensões Elétricas</v>
       </c>
-      <c r="N142" s="34" t="str">
-        <f t="shared" ref="N142:N144" si="74">SUBSTITUTE(CONCATENATE("", E142), ".", " ")</f>
-        <v>Circuitos de Elétrica</v>
-      </c>
-      <c r="O142" s="34" t="str">
-        <f t="shared" ref="O142:O144" si="75">SUBSTITUTE(CONCATENATE("", F142), ".", " ")</f>
-        <v>Conexão de Entrada</v>
-      </c>
-      <c r="P142" s="72" t="s">
-        <v>828</v>
-      </c>
-      <c r="Q142" s="68" t="str">
-        <f t="shared" ref="Q142:Q144" si="76">_xlfn.TRANSLATE(P142,"pt","es")</f>
-        <v>Circuito de entrada para la conexión a la red energética urbana.</v>
-      </c>
-      <c r="R142" s="68" t="str">
-        <f t="shared" ref="R142:R144" si="77">_xlfn.TRANSLATE(P142,"pt","en")</f>
-        <v>Input circuit for connection to the urban energy network.</v>
-      </c>
-      <c r="S142" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T142" s="30" t="str">
-        <f t="shared" ref="T142:T144" si="78">SUBSTITUTE(C142, ".", " ")</f>
-        <v>De Elétrica</v>
-      </c>
-      <c r="U142" s="30" t="str">
-        <f t="shared" ref="U142:U144" si="79">SUBSTITUTE(D142, ".", " ")</f>
-        <v>Tensões Elétricas</v>
-      </c>
-      <c r="V142" s="69" t="str">
-        <f t="shared" ref="V142:V144" si="80">SUBSTITUTE(E142, ".", " ")</f>
-        <v>Circuitos de Elétrica</v>
-      </c>
-      <c r="W142" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="X142" s="59" t="str">
-        <f t="shared" ref="X142:X144" si="81">CONCATENATE("Key-ELET-",A142)</f>
-        <v>Key-ELET-142</v>
-      </c>
-      <c r="Y142" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z142" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA142" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB142" s="70" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC142" s="70" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="58">
-        <v>143</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C143" s="63" t="s">
-        <v>787</v>
-      </c>
-      <c r="D143" s="63" t="s">
-        <v>842</v>
-      </c>
-      <c r="E143" s="63" t="s">
-        <v>844</v>
-      </c>
-      <c r="F143" s="63" t="s">
-        <v>827</v>
-      </c>
-      <c r="G143" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="H143" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="I143" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="J143" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="K143" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="L143" s="34" t="str">
-        <f t="shared" ref="L143" si="82">SUBSTITUTE(CONCATENATE("", C143), ".", " ")</f>
-        <v>De Elétrica</v>
-      </c>
-      <c r="M143" s="34" t="str">
-        <f t="shared" ref="M143" si="83">SUBSTITUTE(CONCATENATE("", D143), ".", " ")</f>
-        <v>Tensões Elétricas</v>
-      </c>
-      <c r="N143" s="34" t="str">
-        <f t="shared" ref="N143" si="84">SUBSTITUTE(CONCATENATE("", E143), ".", " ")</f>
-        <v>Circuitos de Elétrica</v>
-      </c>
-      <c r="O143" s="34" t="str">
-        <f t="shared" ref="O143" si="85">SUBSTITUTE(CONCATENATE("", F143), ".", " ")</f>
-        <v>Circuito Condomínio</v>
-      </c>
-      <c r="P143" s="72" t="s">
-        <v>829</v>
-      </c>
-      <c r="Q143" s="68" t="str">
-        <f t="shared" ref="Q143" si="86">_xlfn.TRANSLATE(P143,"pt","es")</f>
-        <v>Circuito distribuidor de condominios.</v>
-      </c>
-      <c r="R143" s="68" t="str">
-        <f t="shared" ref="R143" si="87">_xlfn.TRANSLATE(P143,"pt","en")</f>
-        <v>Condominium distributor circuit.</v>
-      </c>
-      <c r="S143" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T143" s="30" t="str">
-        <f t="shared" ref="T143" si="88">SUBSTITUTE(C143, ".", " ")</f>
-        <v>De Elétrica</v>
-      </c>
-      <c r="U143" s="30" t="str">
-        <f t="shared" ref="U143" si="89">SUBSTITUTE(D143, ".", " ")</f>
-        <v>Tensões Elétricas</v>
-      </c>
       <c r="V143" s="69" t="str">
-        <f t="shared" ref="V143" si="90">SUBSTITUTE(E143, ".", " ")</f>
+        <f t="shared" si="76"/>
         <v>Circuitos de Elétrica</v>
       </c>
       <c r="W143" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X143" s="59" t="str">
-        <f t="shared" ref="X143" si="91">CONCATENATE("Key-ELET-",A143)</f>
+        <f t="shared" si="77"/>
         <v>Key-ELET-143</v>
       </c>
       <c r="Y143" s="29" t="s">
@@ -18649,8 +19168,11 @@
       <c r="AC143" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD143" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="144" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="58">
         <v>144</v>
       </c>
@@ -18658,16 +19180,16 @@
         <v>781</v>
       </c>
       <c r="C144" s="63" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D144" s="63" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E144" s="63" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="F144" s="63" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="G144" s="62" t="s">
         <v>9</v>
@@ -18685,52 +19207,52 @@
         <v>9</v>
       </c>
       <c r="L144" s="34" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" ref="L144" si="88">SUBSTITUTE(CONCATENATE("", C144), ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="M144" s="34" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" ref="M144" si="89">SUBSTITUTE(CONCATENATE("", D144), ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="N144" s="34" t="str">
-        <f t="shared" si="74"/>
-        <v>Circuitos de Elétrica</v>
+        <f t="shared" ref="N144" si="90">SUBSTITUTE(CONCATENATE("", E144), ".", " ")</f>
+        <v>Pontos de Elétrica</v>
       </c>
       <c r="O144" s="34" t="str">
-        <f t="shared" si="75"/>
-        <v>Circuito Unidade</v>
+        <f t="shared" ref="O144" si="91">SUBSTITUTE(CONCATENATE("", F144), ".", " ")</f>
+        <v>Ponto de Luz</v>
       </c>
       <c r="P144" s="72" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="Q144" s="68" t="str">
-        <f t="shared" si="76"/>
-        <v>Circuito distribuidor de condominios.</v>
+        <f t="shared" ref="Q144" si="92">_xlfn.TRANSLATE(P144,"pt","es")</f>
+        <v>Circuito de iluminación de una unidad residencial o comercial.</v>
       </c>
       <c r="R144" s="68" t="str">
-        <f t="shared" si="77"/>
-        <v>Condominium distributor circuit.</v>
+        <f t="shared" ref="R144" si="93">_xlfn.TRANSLATE(P144,"pt","en")</f>
+        <v>Lighting circuit of a residential or commercial unit.</v>
       </c>
       <c r="S144" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T144" s="30" t="str">
-        <f t="shared" si="78"/>
+        <f t="shared" ref="T144" si="94">SUBSTITUTE(C144, ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="U144" s="30" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" ref="U144" si="95">SUBSTITUTE(D144, ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="V144" s="69" t="str">
-        <f t="shared" si="80"/>
-        <v>Circuitos de Elétrica</v>
+        <f t="shared" ref="V144" si="96">SUBSTITUTE(E144, ".", " ")</f>
+        <v>Pontos de Elétrica</v>
       </c>
       <c r="W144" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X144" s="59" t="str">
-        <f t="shared" si="81"/>
+        <f t="shared" ref="X144" si="97">CONCATENATE("Key-ELET-",A144)</f>
         <v>Key-ELET-144</v>
       </c>
       <c r="Y144" s="29" t="s">
@@ -18740,7 +19262,7 @@
         <v>9</v>
       </c>
       <c r="AA144" s="29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AB144" s="70" t="s">
         <v>9</v>
@@ -18748,8 +19270,11 @@
       <c r="AC144" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD144" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="145" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="58">
         <v>145</v>
       </c>
@@ -18757,16 +19282,16 @@
         <v>781</v>
       </c>
       <c r="C145" s="63" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D145" s="63" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E145" s="63" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F145" s="63" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="G145" s="62" t="s">
         <v>9</v>
@@ -18784,52 +19309,52 @@
         <v>9</v>
       </c>
       <c r="L145" s="34" t="str">
-        <f t="shared" ref="L145" si="92">SUBSTITUTE(CONCATENATE("", C145), ".", " ")</f>
+        <f t="shared" ref="L145:O151" si="98">SUBSTITUTE(CONCATENATE("", C145), ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="M145" s="34" t="str">
-        <f t="shared" ref="M145" si="93">SUBSTITUTE(CONCATENATE("", D145), ".", " ")</f>
+        <f t="shared" ref="M145:M146" si="99">SUBSTITUTE(CONCATENATE("", D145), ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="N145" s="34" t="str">
-        <f t="shared" ref="N145" si="94">SUBSTITUTE(CONCATENATE("", E145), ".", " ")</f>
+        <f t="shared" ref="N145:N146" si="100">SUBSTITUTE(CONCATENATE("", E145), ".", " ")</f>
         <v>Pontos de Elétrica</v>
       </c>
       <c r="O145" s="34" t="str">
-        <f t="shared" ref="O145" si="95">SUBSTITUTE(CONCATENATE("", F145), ".", " ")</f>
-        <v>Ponto de Luz</v>
+        <f t="shared" ref="O145:O146" si="101">SUBSTITUTE(CONCATENATE("", F145), ".", " ")</f>
+        <v>Tomada TUE</v>
       </c>
       <c r="P145" s="72" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="Q145" s="68" t="str">
-        <f t="shared" ref="Q145" si="96">_xlfn.TRANSLATE(P145,"pt","es")</f>
-        <v>Circuito de iluminación de una unidad residencial o comercial.</v>
+        <f t="shared" ref="Q145:Q146" si="102">_xlfn.TRANSLATE(P145,"pt","es")</f>
+        <v>Circuito de uso específico (duchas, aire acondicionado, etc.) de una unidad residencial o comercial.</v>
       </c>
       <c r="R145" s="68" t="str">
-        <f t="shared" ref="R145" si="97">_xlfn.TRANSLATE(P145,"pt","en")</f>
-        <v>Lighting circuit of a residential or commercial unit.</v>
+        <f t="shared" ref="R145:R146" si="103">_xlfn.TRANSLATE(P145,"pt","en")</f>
+        <v>Circuit of specific use sockets (Showers, Air conditioning, etc.) of a residential or commercial unit.</v>
       </c>
       <c r="S145" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T145" s="30" t="str">
-        <f t="shared" ref="T145" si="98">SUBSTITUTE(C145, ".", " ")</f>
+        <f t="shared" ref="T145:V151" si="104">SUBSTITUTE(C145, ".", " ")</f>
         <v>De Elétrica</v>
       </c>
       <c r="U145" s="30" t="str">
-        <f t="shared" ref="U145" si="99">SUBSTITUTE(D145, ".", " ")</f>
+        <f t="shared" ref="U145:U146" si="105">SUBSTITUTE(D145, ".", " ")</f>
         <v>Tensões Elétricas</v>
       </c>
       <c r="V145" s="69" t="str">
-        <f t="shared" ref="V145" si="100">SUBSTITUTE(E145, ".", " ")</f>
+        <f t="shared" ref="V145:V146" si="106">SUBSTITUTE(E145, ".", " ")</f>
         <v>Pontos de Elétrica</v>
       </c>
       <c r="W145" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X145" s="59" t="str">
-        <f t="shared" ref="X145" si="101">CONCATENATE("Key-ELET-",A145)</f>
+        <f t="shared" ref="X145:X151" si="107">CONCATENATE("Key-ELET-",A145)</f>
         <v>Key-ELET-145</v>
       </c>
       <c r="Y145" s="29" t="s">
@@ -18839,7 +19364,7 @@
         <v>9</v>
       </c>
       <c r="AA145" s="29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AB145" s="70" t="s">
         <v>9</v>
@@ -18847,8 +19372,11 @@
       <c r="AC145" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD145" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="146" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="58">
         <v>146</v>
       </c>
@@ -18856,16 +19384,16 @@
         <v>781</v>
       </c>
       <c r="C146" s="63" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D146" s="63" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E146" s="63" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F146" s="63" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G146" s="62" t="s">
         <v>9</v>
@@ -18883,52 +19411,52 @@
         <v>9</v>
       </c>
       <c r="L146" s="34" t="str">
-        <f t="shared" ref="L146:L147" si="102">SUBSTITUTE(CONCATENATE("", C146), ".", " ")</f>
+        <f t="shared" si="98"/>
         <v>De Elétrica</v>
       </c>
       <c r="M146" s="34" t="str">
-        <f t="shared" ref="M146:M147" si="103">SUBSTITUTE(CONCATENATE("", D146), ".", " ")</f>
+        <f t="shared" si="99"/>
         <v>Tensões Elétricas</v>
       </c>
       <c r="N146" s="34" t="str">
-        <f t="shared" ref="N146:N147" si="104">SUBSTITUTE(CONCATENATE("", E146), ".", " ")</f>
+        <f t="shared" si="100"/>
         <v>Pontos de Elétrica</v>
       </c>
       <c r="O146" s="34" t="str">
-        <f t="shared" ref="O146:O147" si="105">SUBSTITUTE(CONCATENATE("", F146), ".", " ")</f>
-        <v>Tomada TUE</v>
+        <f t="shared" si="101"/>
+        <v>Tomada TUG</v>
       </c>
       <c r="P146" s="72" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="Q146" s="68" t="str">
-        <f t="shared" ref="Q146:Q147" si="106">_xlfn.TRANSLATE(P146,"pt","es")</f>
-        <v>Circuito de uso específico (duchas, aire acondicionado, etc.) de una unidad residencial o comercial.</v>
+        <f t="shared" si="102"/>
+        <v>Un circuito de enchufes de uso general (electrodomésticos) de una unidad residencial o comercial.</v>
       </c>
       <c r="R146" s="68" t="str">
-        <f t="shared" ref="R146:R147" si="107">_xlfn.TRANSLATE(P146,"pt","en")</f>
-        <v>Circuit of specific use sockets (Showers, Air conditioning, etc.) of a residential or commercial unit.</v>
+        <f t="shared" si="103"/>
+        <v>A circuit of general purpose outlets (household appliances) of a residential or commercial unit.</v>
       </c>
       <c r="S146" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T146" s="30" t="str">
-        <f t="shared" ref="T146:T147" si="108">SUBSTITUTE(C146, ".", " ")</f>
+        <f t="shared" si="104"/>
         <v>De Elétrica</v>
       </c>
       <c r="U146" s="30" t="str">
-        <f t="shared" ref="U146:U147" si="109">SUBSTITUTE(D146, ".", " ")</f>
+        <f t="shared" si="105"/>
         <v>Tensões Elétricas</v>
       </c>
       <c r="V146" s="69" t="str">
-        <f t="shared" ref="V146:V147" si="110">SUBSTITUTE(E146, ".", " ")</f>
+        <f t="shared" si="106"/>
         <v>Pontos de Elétrica</v>
       </c>
       <c r="W146" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X146" s="59" t="str">
-        <f t="shared" ref="X146:X147" si="111">CONCATENATE("Key-ELET-",A146)</f>
+        <f t="shared" si="107"/>
         <v>Key-ELET-146</v>
       </c>
       <c r="Y146" s="29" t="s">
@@ -18946,8 +19474,11 @@
       <c r="AC146" s="70" t="s">
         <v>9</v>
       </c>
+      <c r="AD146" s="70" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="147" spans="1:29" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="58">
         <v>147</v>
       </c>
@@ -18955,16 +19486,16 @@
         <v>781</v>
       </c>
       <c r="C147" s="63" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="D147" s="63" t="s">
-        <v>842</v>
+        <v>784</v>
       </c>
       <c r="E147" s="63" t="s">
-        <v>843</v>
+        <v>783</v>
       </c>
       <c r="F147" s="63" t="s">
-        <v>826</v>
+        <v>856</v>
       </c>
       <c r="G147" s="62" t="s">
         <v>9</v>
@@ -18982,232 +19513,639 @@
         <v>9</v>
       </c>
       <c r="L147" s="34" t="str">
-        <f t="shared" si="102"/>
-        <v>De Elétrica</v>
+        <f t="shared" si="98"/>
+        <v>De API</v>
       </c>
       <c r="M147" s="34" t="str">
-        <f t="shared" si="103"/>
-        <v>Tensões Elétricas</v>
+        <f t="shared" si="98"/>
+        <v>Macros</v>
       </c>
       <c r="N147" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O147" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P147" s="30" t="s">
+        <v>857</v>
+      </c>
+      <c r="Q147" s="30" t="s">
+        <v>858</v>
+      </c>
+      <c r="R147" s="30" t="s">
+        <v>859</v>
+      </c>
+      <c r="S147" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T147" s="30" t="str">
         <f t="shared" si="104"/>
-        <v>Pontos de Elétrica</v>
-      </c>
-      <c r="O147" s="34" t="str">
-        <f t="shared" si="105"/>
-        <v>Tomada TUG</v>
-      </c>
-      <c r="P147" s="72" t="s">
-        <v>832</v>
-      </c>
-      <c r="Q147" s="68" t="str">
-        <f t="shared" si="106"/>
-        <v>Un circuito de enchufes de uso general (electrodomésticos) de una unidad residencial o comercial.</v>
-      </c>
-      <c r="R147" s="68" t="str">
-        <f t="shared" si="107"/>
-        <v>A circuit of general purpose outlets (household appliances) of a residential or commercial unit.</v>
-      </c>
-      <c r="S147" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T147" s="30" t="str">
-        <f t="shared" si="108"/>
-        <v>De Elétrica</v>
+        <v>De API</v>
       </c>
       <c r="U147" s="30" t="str">
-        <f t="shared" si="109"/>
-        <v>Tensões Elétricas</v>
+        <f t="shared" si="104"/>
+        <v>Macros</v>
       </c>
       <c r="V147" s="69" t="str">
-        <f t="shared" si="110"/>
-        <v>Pontos de Elétrica</v>
+        <f t="shared" si="104"/>
+        <v>Métodos</v>
       </c>
       <c r="W147" s="30" t="s">
         <v>108</v>
       </c>
       <c r="X147" s="59" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="107"/>
         <v>Key-ELET-147</v>
       </c>
-      <c r="Y147" s="29" t="s">
-        <v>103</v>
+      <c r="Y147" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="Z147" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="AA147" s="29" t="s">
-        <v>105</v>
+      <c r="AA147" s="70" t="s">
+        <v>9</v>
       </c>
       <c r="AB147" s="70" t="s">
         <v>9</v>
       </c>
       <c r="AC147" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD147" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="58">
+        <v>148</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C148" s="63" t="s">
+        <v>782</v>
+      </c>
+      <c r="D148" s="63" t="s">
+        <v>784</v>
+      </c>
+      <c r="E148" s="63" t="s">
+        <v>783</v>
+      </c>
+      <c r="F148" s="63" t="s">
+        <v>860</v>
+      </c>
+      <c r="G148" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I148" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J148" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K148" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L148" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>De API</v>
+      </c>
+      <c r="M148" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Macros</v>
+      </c>
+      <c r="N148" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O148" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P148" s="30" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q148" s="30" t="s">
+        <v>862</v>
+      </c>
+      <c r="R148" s="30" t="s">
+        <v>863</v>
+      </c>
+      <c r="S148" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T148" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>De API</v>
+      </c>
+      <c r="U148" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>Macros</v>
+      </c>
+      <c r="V148" s="69" t="str">
+        <f t="shared" si="104"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W148" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="X148" s="59" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-ELET-148</v>
+      </c>
+      <c r="Y148" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z148" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA148" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB148" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC148" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD148" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="58">
+        <v>149</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C149" s="63" t="s">
+        <v>782</v>
+      </c>
+      <c r="D149" s="63" t="s">
+        <v>784</v>
+      </c>
+      <c r="E149" s="63" t="s">
+        <v>783</v>
+      </c>
+      <c r="F149" s="63" t="s">
+        <v>864</v>
+      </c>
+      <c r="G149" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H149" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I149" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J149" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K149" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L149" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>De API</v>
+      </c>
+      <c r="M149" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Macros</v>
+      </c>
+      <c r="N149" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O149" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P149" s="30" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q149" s="30" t="s">
+        <v>866</v>
+      </c>
+      <c r="R149" s="30" t="s">
+        <v>867</v>
+      </c>
+      <c r="S149" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T149" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>De API</v>
+      </c>
+      <c r="U149" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>Macros</v>
+      </c>
+      <c r="V149" s="69" t="str">
+        <f t="shared" si="104"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W149" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="X149" s="59" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-ELET-149</v>
+      </c>
+      <c r="Y149" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z149" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA149" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB149" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC149" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD149" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="58">
+        <v>150</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C150" s="63" t="s">
+        <v>782</v>
+      </c>
+      <c r="D150" s="63" t="s">
+        <v>784</v>
+      </c>
+      <c r="E150" s="63" t="s">
+        <v>783</v>
+      </c>
+      <c r="F150" s="63" t="s">
+        <v>868</v>
+      </c>
+      <c r="G150" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H150" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I150" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J150" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K150" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L150" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>De API</v>
+      </c>
+      <c r="M150" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Macros</v>
+      </c>
+      <c r="N150" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O150" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P150" s="30" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q150" s="30" t="s">
+        <v>870</v>
+      </c>
+      <c r="R150" s="30" t="s">
+        <v>871</v>
+      </c>
+      <c r="S150" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T150" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>De API</v>
+      </c>
+      <c r="U150" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>Macros</v>
+      </c>
+      <c r="V150" s="69" t="str">
+        <f t="shared" si="104"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W150" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="X150" s="59" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-ELET-150</v>
+      </c>
+      <c r="Y150" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z150" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA150" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB150" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC150" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD150" s="70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:30" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="58">
+        <v>151</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C151" s="63" t="s">
+        <v>782</v>
+      </c>
+      <c r="D151" s="63" t="s">
+        <v>784</v>
+      </c>
+      <c r="E151" s="63" t="s">
+        <v>872</v>
+      </c>
+      <c r="F151" s="63" t="s">
+        <v>873</v>
+      </c>
+      <c r="G151" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H151" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="I151" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J151" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="K151" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L151" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>De API</v>
+      </c>
+      <c r="M151" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Macros</v>
+      </c>
+      <c r="N151" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O151" s="34" t="str">
+        <f t="shared" si="98"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P151" s="30" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q151" s="30" t="s">
+        <v>875</v>
+      </c>
+      <c r="R151" s="30" t="s">
+        <v>876</v>
+      </c>
+      <c r="S151" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T151" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>De API</v>
+      </c>
+      <c r="U151" s="30" t="str">
+        <f t="shared" si="104"/>
+        <v>Macros</v>
+      </c>
+      <c r="V151" s="69" t="str">
+        <f t="shared" si="104"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W151" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="X151" s="59" t="str">
+        <f t="shared" si="107"/>
+        <v>Key-ELET-151</v>
+      </c>
+      <c r="Y151" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z151" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA151" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB151" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC151" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD151" s="70" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC217">
-    <sortCondition ref="F2:F217"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC216">
+    <sortCondition ref="F2:F216"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B147">
-    <cfRule type="cellIs" dxfId="84" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B151">
+    <cfRule type="cellIs" dxfId="86" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E151:F151">
+    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="83" priority="1851"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="1855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="82" priority="1864"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="1868"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20:F33">
-    <cfRule type="duplicateValues" dxfId="81" priority="2213"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="2217"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F39">
-    <cfRule type="duplicateValues" dxfId="80" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F41">
-    <cfRule type="duplicateValues" dxfId="76" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="81"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F42:F49">
-    <cfRule type="duplicateValues" dxfId="73" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="duplicateValues" dxfId="69" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="90"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="duplicateValues" dxfId="68" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52">
-    <cfRule type="duplicateValues" dxfId="64" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="95"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="duplicateValues" dxfId="60" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="duplicateValues" dxfId="56" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F59 F42:F49">
-    <cfRule type="duplicateValues" dxfId="52" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F61 F42:F50">
-    <cfRule type="duplicateValues" dxfId="51" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60:F61">
-    <cfRule type="duplicateValues" dxfId="49" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88:F93">
-    <cfRule type="duplicateValues" dxfId="48" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="272"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F94:F102">
-    <cfRule type="duplicateValues" dxfId="40" priority="1912"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1916"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F104">
-    <cfRule type="duplicateValues" dxfId="39" priority="1974"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="1978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F119:F136 F104">
-    <cfRule type="duplicateValues" dxfId="38" priority="2063"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2067"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F136 F104">
-    <cfRule type="duplicateValues" dxfId="37" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="391"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F136">
-    <cfRule type="duplicateValues" dxfId="36" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="388"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F137">
-    <cfRule type="duplicateValues" dxfId="35" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="327"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F138:F147">
-    <cfRule type="duplicateValues" dxfId="34" priority="14"/>
+  <conditionalFormatting sqref="F138:F146">
+    <cfRule type="duplicateValues" dxfId="35" priority="2242"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F148:F1048576 F1:F137">
-    <cfRule type="duplicateValues" dxfId="33" priority="55"/>
+  <conditionalFormatting sqref="F147:F150">
+    <cfRule type="duplicateValues" dxfId="34" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F148:F1048576 F62:F80 F1:F33 F94:F137">
-    <cfRule type="duplicateValues" dxfId="32" priority="2218"/>
+  <conditionalFormatting sqref="F152:F1048576 F1:F137">
+    <cfRule type="duplicateValues" dxfId="33" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F148:F1048576 F119:F137 F104 F94:F102 F62:F80 F1:F33">
-    <cfRule type="duplicateValues" dxfId="31" priority="2224"/>
+  <conditionalFormatting sqref="F152:F1048576 F62:F80 F1:F33 F94:F137">
+    <cfRule type="duplicateValues" dxfId="32" priority="2222"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F148:F1048576 F137 F62 F7:F19">
-    <cfRule type="duplicateValues" dxfId="30" priority="2235"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="2232"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="2233"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="2234"/>
+  <conditionalFormatting sqref="F152:F1048576 F119:F137 F104 F94:F102 F62:F80 F1:F33">
+    <cfRule type="duplicateValues" dxfId="31" priority="2228"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:O1 A1:D1 S1:Y1 AC1">
-    <cfRule type="cellIs" dxfId="26" priority="415" operator="equal">
+  <conditionalFormatting sqref="F152:F1048576 F137 F62 F7:F19">
+    <cfRule type="duplicateValues" dxfId="30" priority="2236"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="2237"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="2238"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="2239"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:O1 A1:D1 S1:Y1 AC1:AD1">
+    <cfRule type="cellIs" dxfId="26" priority="419" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P139:P141">
-    <cfRule type="duplicateValues" dxfId="25" priority="8"/>
+  <conditionalFormatting sqref="P138:P140">
+    <cfRule type="duplicateValues" dxfId="25" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P142:P147">
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+  <conditionalFormatting sqref="P141:P146">
+    <cfRule type="duplicateValues" dxfId="24" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q138:Q147">
-    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+  <conditionalFormatting sqref="Q138:Q146">
+    <cfRule type="duplicateValues" dxfId="23" priority="2264"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2265"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2266"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R34:R61">
-    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="23" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R80:R87">
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28"/>
     <cfRule type="duplicateValues" dxfId="13" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R88:R93">
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R138:R147">
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+  <conditionalFormatting sqref="R138:R146">
+    <cfRule type="duplicateValues" dxfId="11" priority="2268"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2269"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2270"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2271"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7:Y33 Y62:Y137">
-    <cfRule type="containsText" dxfId="7" priority="242" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="246" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",Y7)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19222,15 +20160,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -19295,7 +20233,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -19378,15 +20316,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -19409,7 +20347,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -19465,36 +20403,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:AI18"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="7.53515625" customWidth="1"/>
-    <col min="6" max="6" width="5.3046875" customWidth="1"/>
-    <col min="7" max="7" width="36.69140625" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" customWidth="1"/>
+    <col min="7" max="7" width="36.7109375" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="6.69140625" customWidth="1"/>
-    <col min="10" max="10" width="7.3828125" customWidth="1"/>
-    <col min="11" max="11" width="10.3046875" customWidth="1"/>
-    <col min="12" max="12" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.3046875" customWidth="1"/>
-    <col min="14" max="14" width="6.69140625" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="4.84375" customWidth="1"/>
-    <col min="17" max="17" width="6.3046875" customWidth="1"/>
-    <col min="18" max="19" width="5.69140625" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" customWidth="1"/>
+    <col min="18" max="19" width="5.7109375" customWidth="1"/>
     <col min="20" max="20" width="3" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="4.69140625" customWidth="1"/>
-    <col min="23" max="23" width="11.69140625" customWidth="1"/>
-    <col min="24" max="24" width="6.84375" customWidth="1"/>
-    <col min="25" max="25" width="7.84375" customWidth="1"/>
-    <col min="26" max="35" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.7109375" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" customWidth="1"/>
+    <col min="24" max="24" width="6.85546875" customWidth="1"/>
+    <col min="25" max="25" width="7.85546875" customWidth="1"/>
+    <col min="26" max="35" width="2.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -19601,7 +20539,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -19609,7 +20547,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>9</v>
@@ -19660,10 +20598,10 @@
         <v>9</v>
       </c>
       <c r="T2" s="49" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="V2" s="49" t="s">
         <v>9</v>
@@ -19708,15 +20646,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>81</v>
@@ -19728,13 +20666,13 @@
         <v>76</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="J3" s="49" t="s">
         <v>9</v>
@@ -19767,16 +20705,16 @@
         <v>9</v>
       </c>
       <c r="T3" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U3" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V3" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U3" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V3" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W3" s="76" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="X3" s="77" t="s">
         <v>9</v>
@@ -19815,33 +20753,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E4" s="53" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="J4" s="49" t="s">
         <v>9</v>
@@ -19874,16 +20812,16 @@
         <v>9</v>
       </c>
       <c r="T4" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V4" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U4" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V4" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W4" s="76" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="X4" s="77" t="s">
         <v>9</v>
@@ -19922,76 +20860,76 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="I5" s="24" t="s">
+        <v>816</v>
+      </c>
+      <c r="J5" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="R5" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U5" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V5" s="49" t="s">
+        <v>793</v>
+      </c>
+      <c r="W5" s="76" t="s">
         <v>818</v>
       </c>
-      <c r="J5" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="R5" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T5" s="49" t="s">
-        <v>793</v>
-      </c>
-      <c r="U5" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V5" s="49" t="s">
-        <v>795</v>
-      </c>
-      <c r="W5" s="76" t="s">
-        <v>820</v>
-      </c>
       <c r="X5" s="77" t="s">
         <v>9</v>
       </c>
@@ -20029,27 +20967,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>5</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C6" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E6" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>9</v>
@@ -20088,16 +21026,16 @@
         <v>716</v>
       </c>
       <c r="T6" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U6" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V6" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U6" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V6" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W6" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X6" s="77" t="s">
         <v>9</v>
@@ -20136,27 +21074,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>6</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C7" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E7" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>9</v>
@@ -20195,16 +21133,16 @@
         <v>716</v>
       </c>
       <c r="T7" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U7" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V7" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U7" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V7" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W7" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X7" s="77" t="s">
         <v>9</v>
@@ -20243,27 +21181,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>7</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E8" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H8" s="49" t="s">
         <v>9</v>
@@ -20302,16 +21240,16 @@
         <v>716</v>
       </c>
       <c r="T8" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U8" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V8" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U8" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V8" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W8" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X8" s="77" t="s">
         <v>9</v>
@@ -20350,27 +21288,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>8</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H9" s="49" t="s">
         <v>9</v>
@@ -20409,75 +21347,75 @@
         <v>716</v>
       </c>
       <c r="T9" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U9" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V9" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U9" s="24" t="s">
+      <c r="W9" s="76" t="s">
+        <v>812</v>
+      </c>
+      <c r="X9" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG9" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH9" s="73" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>851</v>
+      </c>
+      <c r="C10" s="54" t="s">
+        <v>824</v>
+      </c>
+      <c r="D10" s="50" t="s">
         <v>819</v>
       </c>
-      <c r="V9" s="49" t="s">
-        <v>795</v>
-      </c>
-      <c r="W9" s="76" t="s">
-        <v>814</v>
-      </c>
-      <c r="X9" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y9" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z9" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB9" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD9" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF9" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG9" s="74" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH9" s="73" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI9" s="74" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20">
-        <v>9</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>826</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>821</v>
-      </c>
       <c r="E10" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H10" s="49" t="s">
         <v>9</v>
@@ -20516,16 +21454,16 @@
         <v>716</v>
       </c>
       <c r="T10" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U10" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V10" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U10" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V10" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W10" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X10" s="77" t="s">
         <v>9</v>
@@ -20564,27 +21502,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>10</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>9</v>
@@ -20623,16 +21561,16 @@
         <v>716</v>
       </c>
       <c r="T11" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U11" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V11" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U11" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V11" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W11" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X11" s="77" t="s">
         <v>9</v>
@@ -20671,27 +21609,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>11</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H12" s="49" t="s">
         <v>9</v>
@@ -20730,16 +21668,16 @@
         <v>716</v>
       </c>
       <c r="T12" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U12" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V12" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U12" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V12" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W12" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X12" s="77" t="s">
         <v>9</v>
@@ -20778,27 +21716,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>12</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="H13" s="49" t="s">
         <v>9</v>
@@ -20837,16 +21775,16 @@
         <v>716</v>
       </c>
       <c r="T13" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U13" s="24" t="s">
+        <v>817</v>
+      </c>
+      <c r="V13" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U13" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="V13" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W13" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="X13" s="77" t="s">
         <v>9</v>
@@ -20885,15 +21823,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>13</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>791</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>785</v>
+        <v>789</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>868</v>
       </c>
       <c r="D14" s="73" t="s">
         <v>9</v>
@@ -20905,62 +21843,62 @@
         <v>76</v>
       </c>
       <c r="G14" s="76" t="s">
+        <v>790</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="M14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="O14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="P14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="R14" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="S14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U14" s="24" t="s">
         <v>792</v>
       </c>
-      <c r="H14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="M14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="N14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="O14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="P14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="R14" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T14" s="49" t="s">
+      <c r="V14" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U14" s="24" t="s">
+      <c r="W14" s="76" t="s">
         <v>794</v>
-      </c>
-      <c r="V14" s="49" t="s">
-        <v>795</v>
-      </c>
-      <c r="W14" s="76" t="s">
-        <v>796</v>
       </c>
       <c r="X14" s="78" t="str">
         <f t="shared" ref="X14:X18" si="0">IF(Y14="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="Y14" s="79" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="Z14" s="73" t="s">
         <v>9</v>
@@ -20993,15 +21931,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>14</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>798</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>785</v>
+        <v>796</v>
+      </c>
+      <c r="C15" s="80" t="s">
+        <v>868</v>
       </c>
       <c r="D15" s="73" t="s">
         <v>9</v>
@@ -21013,7 +21951,7 @@
         <v>76</v>
       </c>
       <c r="G15" s="76" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="H15" s="49" t="s">
         <v>9</v>
@@ -21052,23 +21990,23 @@
         <v>9</v>
       </c>
       <c r="T15" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U15" s="24" t="s">
+        <v>792</v>
+      </c>
+      <c r="V15" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U15" s="24" t="s">
-        <v>794</v>
-      </c>
-      <c r="V15" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W15" s="76" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="X15" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Y15" s="79" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="Z15" s="73" t="s">
         <v>9</v>
@@ -21101,15 +22039,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>15</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>802</v>
-      </c>
-      <c r="C16" s="63" t="s">
-        <v>785</v>
+        <v>800</v>
+      </c>
+      <c r="C16" s="80" t="s">
+        <v>868</v>
       </c>
       <c r="D16" s="73" t="s">
         <v>9</v>
@@ -21121,7 +22059,7 @@
         <v>76</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>9</v>
@@ -21160,23 +22098,23 @@
         <v>9</v>
       </c>
       <c r="T16" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U16" s="24" t="s">
+        <v>792</v>
+      </c>
+      <c r="V16" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U16" s="24" t="s">
-        <v>794</v>
-      </c>
-      <c r="V16" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W16" s="76" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="X16" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Y16" s="79" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="Z16" s="73" t="s">
         <v>9</v>
@@ -21209,15 +22147,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>16</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>806</v>
-      </c>
-      <c r="C17" s="63" t="s">
-        <v>785</v>
+        <v>804</v>
+      </c>
+      <c r="C17" s="80" t="s">
+        <v>868</v>
       </c>
       <c r="D17" s="73" t="s">
         <v>9</v>
@@ -21229,7 +22167,7 @@
         <v>76</v>
       </c>
       <c r="G17" s="76" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="H17" s="49" t="s">
         <v>9</v>
@@ -21268,23 +22206,23 @@
         <v>9</v>
       </c>
       <c r="T17" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U17" s="24" t="s">
+        <v>792</v>
+      </c>
+      <c r="V17" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U17" s="24" t="s">
-        <v>794</v>
-      </c>
-      <c r="V17" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W17" s="76" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="X17" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Y17" s="79" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="Z17" s="73" t="s">
         <v>9</v>
@@ -21317,15 +22255,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:35" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>17</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>810</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>785</v>
+        <v>808</v>
+      </c>
+      <c r="C18" s="80" t="s">
+        <v>868</v>
       </c>
       <c r="D18" s="73" t="s">
         <v>9</v>
@@ -21337,7 +22275,7 @@
         <v>76</v>
       </c>
       <c r="G18" s="76" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="H18" s="49" t="s">
         <v>9</v>
@@ -21376,23 +22314,23 @@
         <v>9</v>
       </c>
       <c r="T18" s="49" t="s">
+        <v>791</v>
+      </c>
+      <c r="U18" s="24" t="s">
+        <v>792</v>
+      </c>
+      <c r="V18" s="49" t="s">
         <v>793</v>
       </c>
-      <c r="U18" s="24" t="s">
-        <v>794</v>
-      </c>
-      <c r="V18" s="49" t="s">
-        <v>795</v>
-      </c>
       <c r="W18" s="76" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="X18" s="78" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="Y18" s="79" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="Z18" s="73" t="s">
         <v>9</v>
